--- a/templates/template_Lakhisarai.xlsx
+++ b/templates/template_Lakhisarai.xlsx
@@ -965,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
         </is>
       </c>
       <c r="D2" s="2">
@@ -1059,6 +1059,42 @@
       </c>
       <c r="I2" s="2">
         <f>'CONSOLIDATED SHEET'!H2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <f>'CONSOLIDATED SHEET'!C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2">
+        <f>'CONSOLIDATED SHEET'!D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="2">
+        <f>'CONSOLIDATED SHEET'!E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <f>'CONSOLIDATED SHEET'!F3</f>
+        <v/>
+      </c>
+      <c r="H3" s="2">
+        <f>'CONSOLIDATED SHEET'!G3</f>
+        <v/>
+      </c>
+      <c r="I3" s="2">
+        <f>'CONSOLIDATED SHEET'!H3</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1214,7 +1250,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1371,7 +1419,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1528,7 +1588,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1685,7 +1757,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1842,7 +1926,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1999,7 +2095,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2156,7 +2264,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2313,7 +2433,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2470,7 +2602,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2627,7 +2771,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z33"/>
+  <dimension ref="A1:AE33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2671,6 +2827,10 @@
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2784,6 +2944,11 @@
           <t>Ankit Kumar</t>
         </is>
       </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2793,7 +2958,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
         </is>
       </c>
       <c r="C2" s="2">
@@ -2892,9 +3057,118 @@
           <t>DBT</t>
         </is>
       </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>Reported By</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>HIV</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>DBT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="C3" s="2">
+        <f>COUNTA('1ST'!C42:C81)+COUNTA('2nd'!C42:C81)+COUNTA('3rd'!C42:C81)+COUNTA('4th'!C42:C81)+COUNTA('5th'!C42:C81)+COUNTA('6th'!C42:C81)+COUNTA('7th'!C42:C81)+COUNTA('8th'!C42:C81)+COUNTA('9th'!C42:C81)+COUNTA('10th'!C42:C81)+COUNTA('11th'!C42:C81)+COUNTA('12th'!C42:C81)+COUNTA('13th'!C42:C81)+COUNTA('14th'!C42:C81)+COUNTA('15th'!C42:C81)+COUNTA('16th'!C42:C81)+COUNTA('17th'!C42:C81)+COUNTA('18th'!C42:C81)+COUNTA('19th'!C42:C81)+COUNTA('20th'!C42:C81)+COUNTA('21st'!C42:C81)+COUNTA('22nd'!C42:C81)+COUNTA('23rd'!C42:C81)+COUNTA('24th'!C42:C81)+COUNTA('25th'!C42:C81)+COUNTA('26th'!C42:C81)+COUNTA('27th'!C42:C81)+COUNTA('28th'!C42:C81)+COUNTA('29th'!C42:C81)+COUNTA('30th'!C42:C81)+COUNTA('31st'!C42:C81)</f>
+        <v/>
+      </c>
+      <c r="D3" s="2">
+        <f>COUNTA('1ST'!D42:D81)+COUNTA('2nd'!D42:D81)+COUNTA('3rd'!D42:D81)+COUNTA('4th'!D42:D81)+COUNTA('5th'!D42:D81)+COUNTA('6th'!D42:D81)+COUNTA('7th'!D42:D81)+COUNTA('8th'!D42:D81)+COUNTA('9th'!D42:D81)+COUNTA('10th'!D42:D81)+COUNTA('11th'!D42:D81)+COUNTA('12th'!D42:D81)+COUNTA('13th'!D42:D81)+COUNTA('14th'!D42:D81)+COUNTA('15th'!D42:D81)+COUNTA('16th'!D42:D81)+COUNTA('17th'!D42:D81)+COUNTA('18th'!D42:D81)+COUNTA('19th'!D42:D81)+COUNTA('20th'!D42:D81)+COUNTA('21st'!D42:D81)+COUNTA('22nd'!D42:D81)+COUNTA('23rd'!D42:D81)+COUNTA('24th'!D42:D81)+COUNTA('25th'!D42:D81)+COUNTA('26th'!D42:D81)+COUNTA('27th'!D42:D81)+COUNTA('28th'!D42:D81)+COUNTA('29th'!D42:D81)+COUNTA('30th'!D42:D81)+COUNTA('31st'!D42:D81)</f>
+        <v/>
+      </c>
+      <c r="E3" s="2">
+        <f>COUNTA('1ST'!E42:E81)+COUNTA('2nd'!E42:E81)+COUNTA('3rd'!E42:E81)+COUNTA('4th'!E42:E81)+COUNTA('5th'!E42:E81)+COUNTA('6th'!E42:E81)+COUNTA('7th'!E42:E81)+COUNTA('8th'!E42:E81)+COUNTA('9th'!E42:E81)+COUNTA('10th'!E42:E81)+COUNTA('11th'!E42:E81)+COUNTA('12th'!E42:E81)+COUNTA('13th'!E42:E81)+COUNTA('14th'!E42:E81)+COUNTA('15th'!E42:E81)+COUNTA('16th'!E42:E81)+COUNTA('17th'!E42:E81)+COUNTA('18th'!E42:E81)+COUNTA('19th'!E42:E81)+COUNTA('20th'!E42:E81)+COUNTA('21st'!E42:E81)+COUNTA('22nd'!E42:E81)+COUNTA('23rd'!E42:E81)+COUNTA('24th'!E42:E81)+COUNTA('25th'!E42:E81)+COUNTA('26th'!E42:E81)+COUNTA('27th'!E42:E81)+COUNTA('28th'!E42:E81)+COUNTA('29th'!E42:E81)+COUNTA('30th'!E42:E81)+COUNTA('31st'!E42:E81)</f>
+        <v/>
+      </c>
+      <c r="F3" s="2">
+        <f>COUNTA('1ST'!F42:F81)+COUNTA('2nd'!F42:F81)+COUNTA('3rd'!F42:F81)+COUNTA('4th'!F42:F81)+COUNTA('5th'!F42:F81)+COUNTA('6th'!F42:F81)+COUNTA('7th'!F42:F81)+COUNTA('8th'!F42:F81)+COUNTA('9th'!F42:F81)+COUNTA('10th'!F42:F81)+COUNTA('11th'!F42:F81)+COUNTA('12th'!F42:F81)+COUNTA('13th'!F42:F81)+COUNTA('14th'!F42:F81)+COUNTA('15th'!F42:F81)+COUNTA('16th'!F42:F81)+COUNTA('17th'!F42:F81)+COUNTA('18th'!F42:F81)+COUNTA('19th'!F42:F81)+COUNTA('20th'!F42:F81)+COUNTA('21st'!F42:F81)+COUNTA('22nd'!F42:F81)+COUNTA('23rd'!F42:F81)+COUNTA('24th'!F42:F81)+COUNTA('25th'!F42:F81)+COUNTA('26th'!F42:F81)+COUNTA('27th'!F42:F81)+COUNTA('28th'!F42:F81)+COUNTA('29th'!F42:F81)+COUNTA('30th'!F42:F81)+COUNTA('31st'!F42:F81)</f>
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <f>COUNTA('1ST'!G42:G81)+COUNTA('2nd'!G42:G81)+COUNTA('3rd'!G42:G81)+COUNTA('4th'!G42:G81)+COUNTA('5th'!G42:G81)+COUNTA('6th'!G42:G81)+COUNTA('7th'!G42:G81)+COUNTA('8th'!G42:G81)+COUNTA('9th'!G42:G81)+COUNTA('10th'!G42:G81)+COUNTA('11th'!G42:G81)+COUNTA('12th'!G42:G81)+COUNTA('13th'!G42:G81)+COUNTA('14th'!G42:G81)+COUNTA('15th'!G42:G81)+COUNTA('16th'!G42:G81)+COUNTA('17th'!G42:G81)+COUNTA('18th'!G42:G81)+COUNTA('19th'!G42:G81)+COUNTA('20th'!G42:G81)+COUNTA('21st'!G42:G81)+COUNTA('22nd'!G42:G81)+COUNTA('23rd'!G42:G81)+COUNTA('24th'!G42:G81)+COUNTA('25th'!G42:G81)+COUNTA('26th'!G42:G81)+COUNTA('27th'!G42:G81)+COUNTA('28th'!G42:G81)+COUNTA('29th'!G42:G81)+COUNTA('30th'!G42:G81)+COUNTA('31st'!G42:G81)</f>
+        <v/>
+      </c>
+      <c r="H3" s="2">
+        <f>COUNTA('1ST'!H42:H81)+COUNTA('2nd'!H42:H81)+COUNTA('3rd'!H42:H81)+COUNTA('4th'!H42:H81)+COUNTA('5th'!H42:H81)+COUNTA('6th'!H42:H81)+COUNTA('7th'!H42:H81)+COUNTA('8th'!H42:H81)+COUNTA('9th'!H42:H81)+COUNTA('10th'!H42:H81)+COUNTA('11th'!H42:H81)+COUNTA('12th'!H42:H81)+COUNTA('13th'!H42:H81)+COUNTA('14th'!H42:H81)+COUNTA('15th'!H42:H81)+COUNTA('16th'!H42:H81)+COUNTA('17th'!H42:H81)+COUNTA('18th'!H42:H81)+COUNTA('19th'!H42:H81)+COUNTA('20th'!H42:H81)+COUNTA('21st'!H42:H81)+COUNTA('22nd'!H42:H81)+COUNTA('23rd'!H42:H81)+COUNTA('24th'!H42:H81)+COUNTA('25th'!H42:H81)+COUNTA('26th'!H42:H81)+COUNTA('27th'!H42:H81)+COUNTA('28th'!H42:H81)+COUNTA('29th'!H42:H81)+COUNTA('30th'!H42:H81)+COUNTA('31st'!H42:H81)</f>
+        <v/>
+      </c>
+      <c r="I3" s="2">
+        <f>COUNTA('1ST'!I42:I81)+COUNTA('2nd'!I42:I81)+COUNTA('3rd'!I42:I81)+COUNTA('4th'!I42:I81)+COUNTA('5th'!I42:I81)+COUNTA('6th'!I42:I81)+COUNTA('7th'!I42:I81)+COUNTA('8th'!I42:I81)+COUNTA('9th'!I42:I81)+COUNTA('10th'!I42:I81)+COUNTA('11th'!I42:I81)+COUNTA('12th'!I42:I81)+COUNTA('13th'!I42:I81)+COUNTA('14th'!I42:I81)+COUNTA('15th'!I42:I81)+COUNTA('16th'!I42:I81)+COUNTA('17th'!I42:I81)+COUNTA('18th'!I42:I81)+COUNTA('19th'!I42:I81)+COUNTA('20th'!I42:I81)+COUNTA('21st'!I42:I81)+COUNTA('22nd'!I42:I81)+COUNTA('23rd'!I42:I81)+COUNTA('24th'!I42:I81)+COUNTA('25th'!I42:I81)+COUNTA('26th'!I42:I81)+COUNTA('27th'!I42:I81)+COUNTA('28th'!I42:I81)+COUNTA('29th'!I42:I81)+COUNTA('30th'!I42:I81)+COUNTA('31st'!I42:I81)</f>
+        <v/>
+      </c>
+      <c r="J3" s="2">
+        <f>COUNTA('1ST'!J42:J81)+COUNTA('2nd'!J42:J81)+COUNTA('3rd'!J42:J81)+COUNTA('4th'!J42:J81)+COUNTA('5th'!J42:J81)+COUNTA('6th'!J42:J81)+COUNTA('7th'!J42:J81)+COUNTA('8th'!J42:J81)+COUNTA('9th'!J42:J81)+COUNTA('10th'!J42:J81)+COUNTA('11th'!J42:J81)+COUNTA('12th'!J42:J81)+COUNTA('13th'!J42:J81)+COUNTA('14th'!J42:J81)+COUNTA('15th'!J42:J81)+COUNTA('16th'!J42:J81)+COUNTA('17th'!J42:J81)+COUNTA('18th'!J42:J81)+COUNTA('19th'!J42:J81)+COUNTA('20th'!J42:J81)+COUNTA('21st'!J42:J81)+COUNTA('22nd'!J42:J81)+COUNTA('23rd'!J42:J81)+COUNTA('24th'!J42:J81)+COUNTA('25th'!J42:J81)+COUNTA('26th'!J42:J81)+COUNTA('27th'!J42:J81)+COUNTA('28th'!J42:J81)+COUNTA('29th'!J42:J81)+COUNTA('30th'!J42:J81)+COUNTA('31st'!J42:J81)</f>
+        <v/>
+      </c>
+      <c r="K3" s="2">
+        <f>COUNTA('1ST'!K42:K81)+COUNTA('2nd'!K42:K81)+COUNTA('3rd'!K42:K81)+COUNTA('4th'!K42:K81)+COUNTA('5th'!K42:K81)+COUNTA('6th'!K42:K81)+COUNTA('7th'!K42:K81)+COUNTA('8th'!K42:K81)+COUNTA('9th'!K42:K81)+COUNTA('10th'!K42:K81)+COUNTA('11th'!K42:K81)+COUNTA('12th'!K42:K81)+COUNTA('13th'!K42:K81)+COUNTA('14th'!K42:K81)+COUNTA('15th'!K42:K81)+COUNTA('16th'!K42:K81)+COUNTA('17th'!K42:K81)+COUNTA('18th'!K42:K81)+COUNTA('19th'!K42:K81)+COUNTA('20th'!K42:K81)+COUNTA('21st'!K42:K81)+COUNTA('22nd'!K42:K81)+COUNTA('23rd'!K42:K81)+COUNTA('24th'!K42:K81)+COUNTA('25th'!K42:K81)+COUNTA('26th'!K42:K81)+COUNTA('27th'!K42:K81)+COUNTA('28th'!K42:K81)+COUNTA('29th'!K42:K81)+COUNTA('30th'!K42:K81)+COUNTA('31st'!K42:K81)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTA('1ST'!L42:L81)+COUNTA('2nd'!L42:L81)+COUNTA('3rd'!L42:L81)+COUNTA('4th'!L42:L81)+COUNTA('5th'!L42:L81)+COUNTA('6th'!L42:L81)+COUNTA('7th'!L42:L81)+COUNTA('8th'!L42:L81)+COUNTA('9th'!L42:L81)+COUNTA('10th'!L42:L81)+COUNTA('11th'!L42:L81)+COUNTA('12th'!L42:L81)+COUNTA('13th'!L42:L81)+COUNTA('14th'!L42:L81)+COUNTA('15th'!L42:L81)+COUNTA('16th'!L42:L81)+COUNTA('17th'!L42:L81)+COUNTA('18th'!L42:L81)+COUNTA('19th'!L42:L81)+COUNTA('20th'!L42:L81)+COUNTA('21st'!L42:L81)+COUNTA('22nd'!L42:L81)+COUNTA('23rd'!L42:L81)+COUNTA('24th'!L42:L81)+COUNTA('25th'!L42:L81)+COUNTA('26th'!L42:L81)+COUNTA('27th'!L42:L81)+COUNTA('28th'!L42:L81)+COUNTA('29th'!L42:L81)+COUNTA('30th'!L42:L81)+COUNTA('31st'!L42:L81)</f>
+        <v/>
+      </c>
+      <c r="M3" s="2">
+        <f>COUNTA('1ST'!M42:M81)+COUNTA('2nd'!M42:M81)+COUNTA('3rd'!M42:M81)+COUNTA('4th'!M42:M81)+COUNTA('5th'!M42:M81)+COUNTA('6th'!M42:M81)+COUNTA('7th'!M42:M81)+COUNTA('8th'!M42:M81)+COUNTA('9th'!M42:M81)+COUNTA('10th'!M42:M81)+COUNTA('11th'!M42:M81)+COUNTA('12th'!M42:M81)+COUNTA('13th'!M42:M81)+COUNTA('14th'!M42:M81)+COUNTA('15th'!M42:M81)+COUNTA('16th'!M42:M81)+COUNTA('17th'!M42:M81)+COUNTA('18th'!M42:M81)+COUNTA('19th'!M42:M81)+COUNTA('20th'!M42:M81)+COUNTA('21st'!M42:M81)+COUNTA('22nd'!M42:M81)+COUNTA('23rd'!M42:M81)+COUNTA('24th'!M42:M81)+COUNTA('25th'!M42:M81)+COUNTA('26th'!M42:M81)+COUNTA('27th'!M42:M81)+COUNTA('28th'!M42:M81)+COUNTA('29th'!M42:M81)+COUNTA('30th'!M42:M81)+COUNTA('31st'!M42:M81)</f>
+        <v/>
+      </c>
+      <c r="N3" s="2">
+        <f>COUNTA('1ST'!N42:N81)+COUNTA('2nd'!N42:N81)+COUNTA('3rd'!N42:N81)+COUNTA('4th'!N42:N81)+COUNTA('5th'!N42:N81)+COUNTA('6th'!N42:N81)+COUNTA('7th'!N42:N81)+COUNTA('8th'!N42:N81)+COUNTA('9th'!N42:N81)+COUNTA('10th'!N42:N81)+COUNTA('11th'!N42:N81)+COUNTA('12th'!N42:N81)+COUNTA('13th'!N42:N81)+COUNTA('14th'!N42:N81)+COUNTA('15th'!N42:N81)+COUNTA('16th'!N42:N81)+COUNTA('17th'!N42:N81)+COUNTA('18th'!N42:N81)+COUNTA('19th'!N42:N81)+COUNTA('20th'!N42:N81)+COUNTA('21st'!N42:N81)+COUNTA('22nd'!N42:N81)+COUNTA('23rd'!N42:N81)+COUNTA('24th'!N42:N81)+COUNTA('25th'!N42:N81)+COUNTA('26th'!N42:N81)+COUNTA('27th'!N42:N81)+COUNTA('28th'!N42:N81)+COUNTA('29th'!N42:N81)+COUNTA('30th'!N42:N81)+COUNTA('31st'!N42:N81)</f>
+        <v/>
+      </c>
+      <c r="O3" s="2">
+        <f>COUNTA('1ST'!O42:O81)+COUNTA('2nd'!O42:O81)+COUNTA('3rd'!O42:O81)+COUNTA('4th'!O42:O81)+COUNTA('5th'!O42:O81)+COUNTA('6th'!O42:O81)+COUNTA('7th'!O42:O81)+COUNTA('8th'!O42:O81)+COUNTA('9th'!O42:O81)+COUNTA('10th'!O42:O81)+COUNTA('11th'!O42:O81)+COUNTA('12th'!O42:O81)+COUNTA('13th'!O42:O81)+COUNTA('14th'!O42:O81)+COUNTA('15th'!O42:O81)+COUNTA('16th'!O42:O81)+COUNTA('17th'!O42:O81)+COUNTA('18th'!O42:O81)+COUNTA('19th'!O42:O81)+COUNTA('20th'!O42:O81)+COUNTA('21st'!O42:O81)+COUNTA('22nd'!O42:O81)+COUNTA('23rd'!O42:O81)+COUNTA('24th'!O42:O81)+COUNTA('25th'!O42:O81)+COUNTA('26th'!O42:O81)+COUNTA('27th'!O42:O81)+COUNTA('28th'!O42:O81)+COUNTA('29th'!O42:O81)+COUNTA('30th'!O42:O81)+COUNTA('31st'!O42:O81)</f>
+        <v/>
+      </c>
+      <c r="P3" s="2">
+        <f>COUNTA('1ST'!P42:P81)+COUNTA('2nd'!P42:P81)+COUNTA('3rd'!P42:P81)+COUNTA('4th'!P42:P81)+COUNTA('5th'!P42:P81)+COUNTA('6th'!P42:P81)+COUNTA('7th'!P42:P81)+COUNTA('8th'!P42:P81)+COUNTA('9th'!P42:P81)+COUNTA('10th'!P42:P81)+COUNTA('11th'!P42:P81)+COUNTA('12th'!P42:P81)+COUNTA('13th'!P42:P81)+COUNTA('14th'!P42:P81)+COUNTA('15th'!P42:P81)+COUNTA('16th'!P42:P81)+COUNTA('17th'!P42:P81)+COUNTA('18th'!P42:P81)+COUNTA('19th'!P42:P81)+COUNTA('20th'!P42:P81)+COUNTA('21st'!P42:P81)+COUNTA('22nd'!P42:P81)+COUNTA('23rd'!P42:P81)+COUNTA('24th'!P42:P81)+COUNTA('25th'!P42:P81)+COUNTA('26th'!P42:P81)+COUNTA('27th'!P42:P81)+COUNTA('28th'!P42:P81)+COUNTA('29th'!P42:P81)+COUNTA('30th'!P42:P81)+COUNTA('31st'!P42:P81)</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>COUNTA('1ST'!Q42:Q81)+COUNTA('2nd'!Q42:Q81)+COUNTA('3rd'!Q42:Q81)+COUNTA('4th'!Q42:Q81)+COUNTA('5th'!Q42:Q81)+COUNTA('6th'!Q42:Q81)+COUNTA('7th'!Q42:Q81)+COUNTA('8th'!Q42:Q81)+COUNTA('9th'!Q42:Q81)+COUNTA('10th'!Q42:Q81)+COUNTA('11th'!Q42:Q81)+COUNTA('12th'!Q42:Q81)+COUNTA('13th'!Q42:Q81)+COUNTA('14th'!Q42:Q81)+COUNTA('15th'!Q42:Q81)+COUNTA('16th'!Q42:Q81)+COUNTA('17th'!Q42:Q81)+COUNTA('18th'!Q42:Q81)+COUNTA('19th'!Q42:Q81)+COUNTA('20th'!Q42:Q81)+COUNTA('21st'!Q42:Q81)+COUNTA('22nd'!Q42:Q81)+COUNTA('23rd'!Q42:Q81)+COUNTA('24th'!Q42:Q81)+COUNTA('25th'!Q42:Q81)+COUNTA('26th'!Q42:Q81)+COUNTA('27th'!Q42:Q81)+COUNTA('28th'!Q42:Q81)+COUNTA('29th'!Q42:Q81)+COUNTA('30th'!Q42:Q81)+COUNTA('31st'!Q42:Q81)</f>
+        <v/>
+      </c>
+      <c r="R3" s="2">
+        <f>COUNTA('1ST'!R42:R81)+COUNTA('2nd'!R42:R81)+COUNTA('3rd'!R42:R81)+COUNTA('4th'!R42:R81)+COUNTA('5th'!R42:R81)+COUNTA('6th'!R42:R81)+COUNTA('7th'!R42:R81)+COUNTA('8th'!R42:R81)+COUNTA('9th'!R42:R81)+COUNTA('10th'!R42:R81)+COUNTA('11th'!R42:R81)+COUNTA('12th'!R42:R81)+COUNTA('13th'!R42:R81)+COUNTA('14th'!R42:R81)+COUNTA('15th'!R42:R81)+COUNTA('16th'!R42:R81)+COUNTA('17th'!R42:R81)+COUNTA('18th'!R42:R81)+COUNTA('19th'!R42:R81)+COUNTA('20th'!R42:R81)+COUNTA('21st'!R42:R81)+COUNTA('22nd'!R42:R81)+COUNTA('23rd'!R42:R81)+COUNTA('24th'!R42:R81)+COUNTA('25th'!R42:R81)+COUNTA('26th'!R42:R81)+COUNTA('27th'!R42:R81)+COUNTA('28th'!R42:R81)+COUNTA('29th'!R42:R81)+COUNTA('30th'!R42:R81)+COUNTA('31st'!R42:R81)</f>
+        <v/>
+      </c>
+      <c r="S3" s="2">
+        <f>COUNTA('1ST'!S42:S81)+COUNTA('2nd'!S42:S81)+COUNTA('3rd'!S42:S81)+COUNTA('4th'!S42:S81)+COUNTA('5th'!S42:S81)+COUNTA('6th'!S42:S81)+COUNTA('7th'!S42:S81)+COUNTA('8th'!S42:S81)+COUNTA('9th'!S42:S81)+COUNTA('10th'!S42:S81)+COUNTA('11th'!S42:S81)+COUNTA('12th'!S42:S81)+COUNTA('13th'!S42:S81)+COUNTA('14th'!S42:S81)+COUNTA('15th'!S42:S81)+COUNTA('16th'!S42:S81)+COUNTA('17th'!S42:S81)+COUNTA('18th'!S42:S81)+COUNTA('19th'!S42:S81)+COUNTA('20th'!S42:S81)+COUNTA('21st'!S42:S81)+COUNTA('22nd'!S42:S81)+COUNTA('23rd'!S42:S81)+COUNTA('24th'!S42:S81)+COUNTA('25th'!S42:S81)+COUNTA('26th'!S42:S81)+COUNTA('27th'!S42:S81)+COUNTA('28th'!S42:S81)+COUNTA('29th'!S42:S81)+COUNTA('30th'!S42:S81)+COUNTA('31st'!S42:S81)</f>
+        <v/>
+      </c>
+      <c r="T3" s="2">
+        <f>COUNTA('1ST'!T42:T81)+COUNTA('2nd'!T42:T81)+COUNTA('3rd'!T42:T81)+COUNTA('4th'!T42:T81)+COUNTA('5th'!T42:T81)+COUNTA('6th'!T42:T81)+COUNTA('7th'!T42:T81)+COUNTA('8th'!T42:T81)+COUNTA('9th'!T42:T81)+COUNTA('10th'!T42:T81)+COUNTA('11th'!T42:T81)+COUNTA('12th'!T42:T81)+COUNTA('13th'!T42:T81)+COUNTA('14th'!T42:T81)+COUNTA('15th'!T42:T81)+COUNTA('16th'!T42:T81)+COUNTA('17th'!T42:T81)+COUNTA('18th'!T42:T81)+COUNTA('19th'!T42:T81)+COUNTA('20th'!T42:T81)+COUNTA('21st'!T42:T81)+COUNTA('22nd'!T42:T81)+COUNTA('23rd'!T42:T81)+COUNTA('24th'!T42:T81)+COUNTA('25th'!T42:T81)+COUNTA('26th'!T42:T81)+COUNTA('27th'!T42:T81)+COUNTA('28th'!T42:T81)+COUNTA('29th'!T42:T81)+COUNTA('30th'!T42:T81)+COUNTA('31st'!T42:T81)</f>
+        <v/>
+      </c>
+      <c r="U3" s="2">
+        <f>COUNTA('1ST'!U42:U81)+COUNTA('2nd'!U42:U81)+COUNTA('3rd'!U42:U81)+COUNTA('4th'!U42:U81)+COUNTA('5th'!U42:U81)+COUNTA('6th'!U42:U81)+COUNTA('7th'!U42:U81)+COUNTA('8th'!U42:U81)+COUNTA('9th'!U42:U81)+COUNTA('10th'!U42:U81)+COUNTA('11th'!U42:U81)+COUNTA('12th'!U42:U81)+COUNTA('13th'!U42:U81)+COUNTA('14th'!U42:U81)+COUNTA('15th'!U42:U81)+COUNTA('16th'!U42:U81)+COUNTA('17th'!U42:U81)+COUNTA('18th'!U42:U81)+COUNTA('19th'!U42:U81)+COUNTA('20th'!U42:U81)+COUNTA('21st'!U42:U81)+COUNTA('22nd'!U42:U81)+COUNTA('23rd'!U42:U81)+COUNTA('24th'!U42:U81)+COUNTA('25th'!U42:U81)+COUNTA('26th'!U42:U81)+COUNTA('27th'!U42:U81)+COUNTA('28th'!U42:U81)+COUNTA('29th'!U42:U81)+COUNTA('30th'!U42:U81)+COUNTA('31st'!U42:U81)</f>
+        <v/>
+      </c>
       <c r="W3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2902,154 +3176,245 @@
       <c r="W4" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="AB4" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="W5" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="AB5" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="W6" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="AB6" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="W7" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="AB7" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="W8" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="AB8" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="W9" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="AB9" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="W10" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="AB10" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="W11" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="AB11" s="4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="W12" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="AB12" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="W13" s="4" t="n">
         <v>11</v>
       </c>
+      <c r="AB13" s="4" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="W14" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="AB14" s="4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="W15" s="4" t="n">
         <v>13</v>
       </c>
+      <c r="AB15" s="4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="W16" s="4" t="n">
         <v>14</v>
       </c>
+      <c r="AB16" s="4" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="W17" s="4" t="n">
         <v>15</v>
       </c>
+      <c r="AB17" s="4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="W18" s="4" t="n">
         <v>16</v>
       </c>
+      <c r="AB18" s="4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
       <c r="W19" s="4" t="n">
         <v>17</v>
       </c>
+      <c r="AB19" s="4" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="20">
       <c r="W20" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="AB20" s="4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="21">
       <c r="W21" s="4" t="n">
         <v>19</v>
       </c>
+      <c r="AB21" s="4" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="22">
       <c r="W22" s="4" t="n">
         <v>20</v>
       </c>
+      <c r="AB22" s="4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="23">
       <c r="W23" s="4" t="n">
         <v>21</v>
       </c>
+      <c r="AB23" s="4" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="24">
       <c r="W24" s="4" t="n">
         <v>22</v>
       </c>
+      <c r="AB24" s="4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="25">
       <c r="W25" s="4" t="n">
         <v>23</v>
       </c>
+      <c r="AB25" s="4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="26">
       <c r="W26" s="4" t="n">
         <v>24</v>
       </c>
+      <c r="AB26" s="4" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="27">
       <c r="W27" s="4" t="n">
         <v>25</v>
       </c>
+      <c r="AB27" s="4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="28">
       <c r="W28" s="4" t="n">
         <v>26</v>
       </c>
+      <c r="AB28" s="4" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="29">
       <c r="W29" s="4" t="n">
         <v>27</v>
       </c>
+      <c r="AB29" s="4" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="30">
       <c r="W30" s="4" t="n">
         <v>28</v>
       </c>
+      <c r="AB30" s="4" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="31">
       <c r="W31" s="4" t="n">
         <v>29</v>
       </c>
+      <c r="AB31" s="4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="32">
       <c r="W32" s="4" t="n">
         <v>30</v>
       </c>
+      <c r="AB32" s="4" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="33">
       <c r="W33" s="4" t="n">
         <v>31</v>
       </c>
+      <c r="AB33" s="4" t="n">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="AB1:AE1"/>
     <mergeCell ref="W1:Z1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3063,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3204,7 +3569,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3361,7 +3738,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3518,7 +3907,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3675,7 +4076,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -3691,7 +4104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3832,7 +4245,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -3848,7 +4273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3989,7 +4414,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4146,7 +4583,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4303,7 +4752,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4460,7 +4921,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4617,7 +5090,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4633,7 +5118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4774,7 +5259,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4790,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4931,7 +5428,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -4947,7 +5456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5088,7 +5597,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5245,7 +5766,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5402,7 +5935,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5559,7 +6104,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -5575,7 +6132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5716,7 +6273,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -5732,7 +6301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5873,7 +6442,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -5889,7 +6470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6030,7 +6611,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6187,7 +6780,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6344,7 +6949,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Field Officer</t>
+          <t>FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Ram Prakash</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FC</t>
         </is>
       </c>
     </row>

--- a/templates/template_Lakhisarai.xlsx
+++ b/templates/template_Lakhisarai.xlsx
@@ -108,12 +108,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -965,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1095,6 +1096,37 @@
       </c>
       <c r="I3" s="2">
         <f>'CONSOLIDATED SHEET'!H3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <f>SUM(D2:D3)</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="3">
+        <f>SUM(G2:G3)</f>
+        <v/>
+      </c>
+      <c r="H4" s="3">
+        <f>SUM(H2:H3)</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>SUM(I2:I3)</f>
         <v/>
       </c>
     </row>
@@ -2939,12 +2971,12 @@
           <t>Consent with ID</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Ankit Kumar</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>Ram Prakash</t>
         </is>
@@ -2962,117 +2994,117 @@
         </is>
       </c>
       <c r="C2" s="2">
-        <f>COUNTA('1ST'!C2:C41)+COUNTA('2nd'!C2:C41)+COUNTA('3rd'!C2:C41)+COUNTA('4th'!C2:C41)+COUNTA('5th'!C2:C41)+COUNTA('6th'!C2:C41)+COUNTA('7th'!C2:C41)+COUNTA('8th'!C2:C41)+COUNTA('9th'!C2:C41)+COUNTA('10th'!C2:C41)+COUNTA('11th'!C2:C41)+COUNTA('12th'!C2:C41)+COUNTA('13th'!C2:C41)+COUNTA('14th'!C2:C41)+COUNTA('15th'!C2:C41)+COUNTA('16th'!C2:C41)+COUNTA('17th'!C2:C41)+COUNTA('18th'!C2:C41)+COUNTA('19th'!C2:C41)+COUNTA('20th'!C2:C41)+COUNTA('21st'!C2:C41)+COUNTA('22nd'!C2:C41)+COUNTA('23rd'!C2:C41)+COUNTA('24th'!C2:C41)+COUNTA('25th'!C2:C41)+COUNTA('26th'!C2:C41)+COUNTA('27th'!C2:C41)+COUNTA('28th'!C2:C41)+COUNTA('29th'!C2:C41)+COUNTA('30th'!C2:C41)+COUNTA('31st'!C2:C41)</f>
+        <f>(COUNTA('1ST'!C2:C41)+COUNTA('2nd'!C2:C41)+COUNTA('3rd'!C2:C41)+COUNTA('4th'!C2:C41)+COUNTA('5th'!C2:C41)+COUNTA('6th'!C2:C41)+COUNTA('7th'!C2:C41)+COUNTA('8th'!C2:C41)+COUNTA('9th'!C2:C41)+COUNTA('10th'!C2:C41)+COUNTA('11th'!C2:C41)+COUNTA('12th'!C2:C41)+COUNTA('13th'!C2:C41)+COUNTA('14th'!C2:C41)+COUNTA('15th'!C2:C41)+COUNTA('16th'!C2:C41)+COUNTA('17th'!C2:C41)+COUNTA('18th'!C2:C41)+COUNTA('19th'!C2:C41)+COUNTA('20th'!C2:C41)+COUNTA('21st'!C2:C41)+COUNTA('22nd'!C2:C41)+COUNTA('23rd'!C2:C41)+COUNTA('24th'!C2:C41)+COUNTA('25th'!C2:C41)+COUNTA('26th'!C2:C41)+COUNTA('27th'!C2:C41)+COUNTA('28th'!C2:C41)+COUNTA('29th'!C2:C41)+COUNTA('30th'!C2:C41)+COUNTA('31st'!C2:C41))+0</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTA('1ST'!D2:D41)+COUNTA('2nd'!D2:D41)+COUNTA('3rd'!D2:D41)+COUNTA('4th'!D2:D41)+COUNTA('5th'!D2:D41)+COUNTA('6th'!D2:D41)+COUNTA('7th'!D2:D41)+COUNTA('8th'!D2:D41)+COUNTA('9th'!D2:D41)+COUNTA('10th'!D2:D41)+COUNTA('11th'!D2:D41)+COUNTA('12th'!D2:D41)+COUNTA('13th'!D2:D41)+COUNTA('14th'!D2:D41)+COUNTA('15th'!D2:D41)+COUNTA('16th'!D2:D41)+COUNTA('17th'!D2:D41)+COUNTA('18th'!D2:D41)+COUNTA('19th'!D2:D41)+COUNTA('20th'!D2:D41)+COUNTA('21st'!D2:D41)+COUNTA('22nd'!D2:D41)+COUNTA('23rd'!D2:D41)+COUNTA('24th'!D2:D41)+COUNTA('25th'!D2:D41)+COUNTA('26th'!D2:D41)+COUNTA('27th'!D2:D41)+COUNTA('28th'!D2:D41)+COUNTA('29th'!D2:D41)+COUNTA('30th'!D2:D41)+COUNTA('31st'!D2:D41)</f>
+        <f>(COUNTA('1ST'!D2:D41)+COUNTA('2nd'!D2:D41)+COUNTA('3rd'!D2:D41)+COUNTA('4th'!D2:D41)+COUNTA('5th'!D2:D41)+COUNTA('6th'!D2:D41)+COUNTA('7th'!D2:D41)+COUNTA('8th'!D2:D41)+COUNTA('9th'!D2:D41)+COUNTA('10th'!D2:D41)+COUNTA('11th'!D2:D41)+COUNTA('12th'!D2:D41)+COUNTA('13th'!D2:D41)+COUNTA('14th'!D2:D41)+COUNTA('15th'!D2:D41)+COUNTA('16th'!D2:D41)+COUNTA('17th'!D2:D41)+COUNTA('18th'!D2:D41)+COUNTA('19th'!D2:D41)+COUNTA('20th'!D2:D41)+COUNTA('21st'!D2:D41)+COUNTA('22nd'!D2:D41)+COUNTA('23rd'!D2:D41)+COUNTA('24th'!D2:D41)+COUNTA('25th'!D2:D41)+COUNTA('26th'!D2:D41)+COUNTA('27th'!D2:D41)+COUNTA('28th'!D2:D41)+COUNTA('29th'!D2:D41)+COUNTA('30th'!D2:D41)+COUNTA('31st'!D2:D41))+0</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>COUNTA('1ST'!E2:E41)+COUNTA('2nd'!E2:E41)+COUNTA('3rd'!E2:E41)+COUNTA('4th'!E2:E41)+COUNTA('5th'!E2:E41)+COUNTA('6th'!E2:E41)+COUNTA('7th'!E2:E41)+COUNTA('8th'!E2:E41)+COUNTA('9th'!E2:E41)+COUNTA('10th'!E2:E41)+COUNTA('11th'!E2:E41)+COUNTA('12th'!E2:E41)+COUNTA('13th'!E2:E41)+COUNTA('14th'!E2:E41)+COUNTA('15th'!E2:E41)+COUNTA('16th'!E2:E41)+COUNTA('17th'!E2:E41)+COUNTA('18th'!E2:E41)+COUNTA('19th'!E2:E41)+COUNTA('20th'!E2:E41)+COUNTA('21st'!E2:E41)+COUNTA('22nd'!E2:E41)+COUNTA('23rd'!E2:E41)+COUNTA('24th'!E2:E41)+COUNTA('25th'!E2:E41)+COUNTA('26th'!E2:E41)+COUNTA('27th'!E2:E41)+COUNTA('28th'!E2:E41)+COUNTA('29th'!E2:E41)+COUNTA('30th'!E2:E41)+COUNTA('31st'!E2:E41)</f>
+        <f>(COUNTA('1ST'!E2:E41)+COUNTA('2nd'!E2:E41)+COUNTA('3rd'!E2:E41)+COUNTA('4th'!E2:E41)+COUNTA('5th'!E2:E41)+COUNTA('6th'!E2:E41)+COUNTA('7th'!E2:E41)+COUNTA('8th'!E2:E41)+COUNTA('9th'!E2:E41)+COUNTA('10th'!E2:E41)+COUNTA('11th'!E2:E41)+COUNTA('12th'!E2:E41)+COUNTA('13th'!E2:E41)+COUNTA('14th'!E2:E41)+COUNTA('15th'!E2:E41)+COUNTA('16th'!E2:E41)+COUNTA('17th'!E2:E41)+COUNTA('18th'!E2:E41)+COUNTA('19th'!E2:E41)+COUNTA('20th'!E2:E41)+COUNTA('21st'!E2:E41)+COUNTA('22nd'!E2:E41)+COUNTA('23rd'!E2:E41)+COUNTA('24th'!E2:E41)+COUNTA('25th'!E2:E41)+COUNTA('26th'!E2:E41)+COUNTA('27th'!E2:E41)+COUNTA('28th'!E2:E41)+COUNTA('29th'!E2:E41)+COUNTA('30th'!E2:E41)+COUNTA('31st'!E2:E41))+0</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTA('1ST'!F2:F41)+COUNTA('2nd'!F2:F41)+COUNTA('3rd'!F2:F41)+COUNTA('4th'!F2:F41)+COUNTA('5th'!F2:F41)+COUNTA('6th'!F2:F41)+COUNTA('7th'!F2:F41)+COUNTA('8th'!F2:F41)+COUNTA('9th'!F2:F41)+COUNTA('10th'!F2:F41)+COUNTA('11th'!F2:F41)+COUNTA('12th'!F2:F41)+COUNTA('13th'!F2:F41)+COUNTA('14th'!F2:F41)+COUNTA('15th'!F2:F41)+COUNTA('16th'!F2:F41)+COUNTA('17th'!F2:F41)+COUNTA('18th'!F2:F41)+COUNTA('19th'!F2:F41)+COUNTA('20th'!F2:F41)+COUNTA('21st'!F2:F41)+COUNTA('22nd'!F2:F41)+COUNTA('23rd'!F2:F41)+COUNTA('24th'!F2:F41)+COUNTA('25th'!F2:F41)+COUNTA('26th'!F2:F41)+COUNTA('27th'!F2:F41)+COUNTA('28th'!F2:F41)+COUNTA('29th'!F2:F41)+COUNTA('30th'!F2:F41)+COUNTA('31st'!F2:F41)</f>
+        <f>(COUNTA('1ST'!F2:F41)+COUNTA('2nd'!F2:F41)+COUNTA('3rd'!F2:F41)+COUNTA('4th'!F2:F41)+COUNTA('5th'!F2:F41)+COUNTA('6th'!F2:F41)+COUNTA('7th'!F2:F41)+COUNTA('8th'!F2:F41)+COUNTA('9th'!F2:F41)+COUNTA('10th'!F2:F41)+COUNTA('11th'!F2:F41)+COUNTA('12th'!F2:F41)+COUNTA('13th'!F2:F41)+COUNTA('14th'!F2:F41)+COUNTA('15th'!F2:F41)+COUNTA('16th'!F2:F41)+COUNTA('17th'!F2:F41)+COUNTA('18th'!F2:F41)+COUNTA('19th'!F2:F41)+COUNTA('20th'!F2:F41)+COUNTA('21st'!F2:F41)+COUNTA('22nd'!F2:F41)+COUNTA('23rd'!F2:F41)+COUNTA('24th'!F2:F41)+COUNTA('25th'!F2:F41)+COUNTA('26th'!F2:F41)+COUNTA('27th'!F2:F41)+COUNTA('28th'!F2:F41)+COUNTA('29th'!F2:F41)+COUNTA('30th'!F2:F41)+COUNTA('31st'!F2:F41))+0</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTA('1ST'!G2:G41)+COUNTA('2nd'!G2:G41)+COUNTA('3rd'!G2:G41)+COUNTA('4th'!G2:G41)+COUNTA('5th'!G2:G41)+COUNTA('6th'!G2:G41)+COUNTA('7th'!G2:G41)+COUNTA('8th'!G2:G41)+COUNTA('9th'!G2:G41)+COUNTA('10th'!G2:G41)+COUNTA('11th'!G2:G41)+COUNTA('12th'!G2:G41)+COUNTA('13th'!G2:G41)+COUNTA('14th'!G2:G41)+COUNTA('15th'!G2:G41)+COUNTA('16th'!G2:G41)+COUNTA('17th'!G2:G41)+COUNTA('18th'!G2:G41)+COUNTA('19th'!G2:G41)+COUNTA('20th'!G2:G41)+COUNTA('21st'!G2:G41)+COUNTA('22nd'!G2:G41)+COUNTA('23rd'!G2:G41)+COUNTA('24th'!G2:G41)+COUNTA('25th'!G2:G41)+COUNTA('26th'!G2:G41)+COUNTA('27th'!G2:G41)+COUNTA('28th'!G2:G41)+COUNTA('29th'!G2:G41)+COUNTA('30th'!G2:G41)+COUNTA('31st'!G2:G41)</f>
+        <f>(COUNTA('1ST'!G2:G41)+COUNTA('2nd'!G2:G41)+COUNTA('3rd'!G2:G41)+COUNTA('4th'!G2:G41)+COUNTA('5th'!G2:G41)+COUNTA('6th'!G2:G41)+COUNTA('7th'!G2:G41)+COUNTA('8th'!G2:G41)+COUNTA('9th'!G2:G41)+COUNTA('10th'!G2:G41)+COUNTA('11th'!G2:G41)+COUNTA('12th'!G2:G41)+COUNTA('13th'!G2:G41)+COUNTA('14th'!G2:G41)+COUNTA('15th'!G2:G41)+COUNTA('16th'!G2:G41)+COUNTA('17th'!G2:G41)+COUNTA('18th'!G2:G41)+COUNTA('19th'!G2:G41)+COUNTA('20th'!G2:G41)+COUNTA('21st'!G2:G41)+COUNTA('22nd'!G2:G41)+COUNTA('23rd'!G2:G41)+COUNTA('24th'!G2:G41)+COUNTA('25th'!G2:G41)+COUNTA('26th'!G2:G41)+COUNTA('27th'!G2:G41)+COUNTA('28th'!G2:G41)+COUNTA('29th'!G2:G41)+COUNTA('30th'!G2:G41)+COUNTA('31st'!G2:G41))+0</f>
         <v/>
       </c>
       <c r="H2" s="2">
-        <f>COUNTA('1ST'!H2:H41)+COUNTA('2nd'!H2:H41)+COUNTA('3rd'!H2:H41)+COUNTA('4th'!H2:H41)+COUNTA('5th'!H2:H41)+COUNTA('6th'!H2:H41)+COUNTA('7th'!H2:H41)+COUNTA('8th'!H2:H41)+COUNTA('9th'!H2:H41)+COUNTA('10th'!H2:H41)+COUNTA('11th'!H2:H41)+COUNTA('12th'!H2:H41)+COUNTA('13th'!H2:H41)+COUNTA('14th'!H2:H41)+COUNTA('15th'!H2:H41)+COUNTA('16th'!H2:H41)+COUNTA('17th'!H2:H41)+COUNTA('18th'!H2:H41)+COUNTA('19th'!H2:H41)+COUNTA('20th'!H2:H41)+COUNTA('21st'!H2:H41)+COUNTA('22nd'!H2:H41)+COUNTA('23rd'!H2:H41)+COUNTA('24th'!H2:H41)+COUNTA('25th'!H2:H41)+COUNTA('26th'!H2:H41)+COUNTA('27th'!H2:H41)+COUNTA('28th'!H2:H41)+COUNTA('29th'!H2:H41)+COUNTA('30th'!H2:H41)+COUNTA('31st'!H2:H41)</f>
+        <f>(COUNTA('1ST'!H2:H41)+COUNTA('2nd'!H2:H41)+COUNTA('3rd'!H2:H41)+COUNTA('4th'!H2:H41)+COUNTA('5th'!H2:H41)+COUNTA('6th'!H2:H41)+COUNTA('7th'!H2:H41)+COUNTA('8th'!H2:H41)+COUNTA('9th'!H2:H41)+COUNTA('10th'!H2:H41)+COUNTA('11th'!H2:H41)+COUNTA('12th'!H2:H41)+COUNTA('13th'!H2:H41)+COUNTA('14th'!H2:H41)+COUNTA('15th'!H2:H41)+COUNTA('16th'!H2:H41)+COUNTA('17th'!H2:H41)+COUNTA('18th'!H2:H41)+COUNTA('19th'!H2:H41)+COUNTA('20th'!H2:H41)+COUNTA('21st'!H2:H41)+COUNTA('22nd'!H2:H41)+COUNTA('23rd'!H2:H41)+COUNTA('24th'!H2:H41)+COUNTA('25th'!H2:H41)+COUNTA('26th'!H2:H41)+COUNTA('27th'!H2:H41)+COUNTA('28th'!H2:H41)+COUNTA('29th'!H2:H41)+COUNTA('30th'!H2:H41)+COUNTA('31st'!H2:H41))+0</f>
         <v/>
       </c>
       <c r="I2" s="2">
-        <f>COUNTA('1ST'!I2:I41)+COUNTA('2nd'!I2:I41)+COUNTA('3rd'!I2:I41)+COUNTA('4th'!I2:I41)+COUNTA('5th'!I2:I41)+COUNTA('6th'!I2:I41)+COUNTA('7th'!I2:I41)+COUNTA('8th'!I2:I41)+COUNTA('9th'!I2:I41)+COUNTA('10th'!I2:I41)+COUNTA('11th'!I2:I41)+COUNTA('12th'!I2:I41)+COUNTA('13th'!I2:I41)+COUNTA('14th'!I2:I41)+COUNTA('15th'!I2:I41)+COUNTA('16th'!I2:I41)+COUNTA('17th'!I2:I41)+COUNTA('18th'!I2:I41)+COUNTA('19th'!I2:I41)+COUNTA('20th'!I2:I41)+COUNTA('21st'!I2:I41)+COUNTA('22nd'!I2:I41)+COUNTA('23rd'!I2:I41)+COUNTA('24th'!I2:I41)+COUNTA('25th'!I2:I41)+COUNTA('26th'!I2:I41)+COUNTA('27th'!I2:I41)+COUNTA('28th'!I2:I41)+COUNTA('29th'!I2:I41)+COUNTA('30th'!I2:I41)+COUNTA('31st'!I2:I41)</f>
+        <f>(COUNTA('1ST'!I2:I41)+COUNTA('2nd'!I2:I41)+COUNTA('3rd'!I2:I41)+COUNTA('4th'!I2:I41)+COUNTA('5th'!I2:I41)+COUNTA('6th'!I2:I41)+COUNTA('7th'!I2:I41)+COUNTA('8th'!I2:I41)+COUNTA('9th'!I2:I41)+COUNTA('10th'!I2:I41)+COUNTA('11th'!I2:I41)+COUNTA('12th'!I2:I41)+COUNTA('13th'!I2:I41)+COUNTA('14th'!I2:I41)+COUNTA('15th'!I2:I41)+COUNTA('16th'!I2:I41)+COUNTA('17th'!I2:I41)+COUNTA('18th'!I2:I41)+COUNTA('19th'!I2:I41)+COUNTA('20th'!I2:I41)+COUNTA('21st'!I2:I41)+COUNTA('22nd'!I2:I41)+COUNTA('23rd'!I2:I41)+COUNTA('24th'!I2:I41)+COUNTA('25th'!I2:I41)+COUNTA('26th'!I2:I41)+COUNTA('27th'!I2:I41)+COUNTA('28th'!I2:I41)+COUNTA('29th'!I2:I41)+COUNTA('30th'!I2:I41)+COUNTA('31st'!I2:I41))+0</f>
         <v/>
       </c>
       <c r="J2" s="2">
-        <f>COUNTA('1ST'!J2:J41)+COUNTA('2nd'!J2:J41)+COUNTA('3rd'!J2:J41)+COUNTA('4th'!J2:J41)+COUNTA('5th'!J2:J41)+COUNTA('6th'!J2:J41)+COUNTA('7th'!J2:J41)+COUNTA('8th'!J2:J41)+COUNTA('9th'!J2:J41)+COUNTA('10th'!J2:J41)+COUNTA('11th'!J2:J41)+COUNTA('12th'!J2:J41)+COUNTA('13th'!J2:J41)+COUNTA('14th'!J2:J41)+COUNTA('15th'!J2:J41)+COUNTA('16th'!J2:J41)+COUNTA('17th'!J2:J41)+COUNTA('18th'!J2:J41)+COUNTA('19th'!J2:J41)+COUNTA('20th'!J2:J41)+COUNTA('21st'!J2:J41)+COUNTA('22nd'!J2:J41)+COUNTA('23rd'!J2:J41)+COUNTA('24th'!J2:J41)+COUNTA('25th'!J2:J41)+COUNTA('26th'!J2:J41)+COUNTA('27th'!J2:J41)+COUNTA('28th'!J2:J41)+COUNTA('29th'!J2:J41)+COUNTA('30th'!J2:J41)+COUNTA('31st'!J2:J41)</f>
+        <f>(COUNTA('1ST'!J2:J41)+COUNTA('2nd'!J2:J41)+COUNTA('3rd'!J2:J41)+COUNTA('4th'!J2:J41)+COUNTA('5th'!J2:J41)+COUNTA('6th'!J2:J41)+COUNTA('7th'!J2:J41)+COUNTA('8th'!J2:J41)+COUNTA('9th'!J2:J41)+COUNTA('10th'!J2:J41)+COUNTA('11th'!J2:J41)+COUNTA('12th'!J2:J41)+COUNTA('13th'!J2:J41)+COUNTA('14th'!J2:J41)+COUNTA('15th'!J2:J41)+COUNTA('16th'!J2:J41)+COUNTA('17th'!J2:J41)+COUNTA('18th'!J2:J41)+COUNTA('19th'!J2:J41)+COUNTA('20th'!J2:J41)+COUNTA('21st'!J2:J41)+COUNTA('22nd'!J2:J41)+COUNTA('23rd'!J2:J41)+COUNTA('24th'!J2:J41)+COUNTA('25th'!J2:J41)+COUNTA('26th'!J2:J41)+COUNTA('27th'!J2:J41)+COUNTA('28th'!J2:J41)+COUNTA('29th'!J2:J41)+COUNTA('30th'!J2:J41)+COUNTA('31st'!J2:J41))+0</f>
         <v/>
       </c>
       <c r="K2" s="2">
-        <f>COUNTA('1ST'!K2:K41)+COUNTA('2nd'!K2:K41)+COUNTA('3rd'!K2:K41)+COUNTA('4th'!K2:K41)+COUNTA('5th'!K2:K41)+COUNTA('6th'!K2:K41)+COUNTA('7th'!K2:K41)+COUNTA('8th'!K2:K41)+COUNTA('9th'!K2:K41)+COUNTA('10th'!K2:K41)+COUNTA('11th'!K2:K41)+COUNTA('12th'!K2:K41)+COUNTA('13th'!K2:K41)+COUNTA('14th'!K2:K41)+COUNTA('15th'!K2:K41)+COUNTA('16th'!K2:K41)+COUNTA('17th'!K2:K41)+COUNTA('18th'!K2:K41)+COUNTA('19th'!K2:K41)+COUNTA('20th'!K2:K41)+COUNTA('21st'!K2:K41)+COUNTA('22nd'!K2:K41)+COUNTA('23rd'!K2:K41)+COUNTA('24th'!K2:K41)+COUNTA('25th'!K2:K41)+COUNTA('26th'!K2:K41)+COUNTA('27th'!K2:K41)+COUNTA('28th'!K2:K41)+COUNTA('29th'!K2:K41)+COUNTA('30th'!K2:K41)+COUNTA('31st'!K2:K41)</f>
+        <f>(COUNTA('1ST'!K2:K41)+COUNTA('2nd'!K2:K41)+COUNTA('3rd'!K2:K41)+COUNTA('4th'!K2:K41)+COUNTA('5th'!K2:K41)+COUNTA('6th'!K2:K41)+COUNTA('7th'!K2:K41)+COUNTA('8th'!K2:K41)+COUNTA('9th'!K2:K41)+COUNTA('10th'!K2:K41)+COUNTA('11th'!K2:K41)+COUNTA('12th'!K2:K41)+COUNTA('13th'!K2:K41)+COUNTA('14th'!K2:K41)+COUNTA('15th'!K2:K41)+COUNTA('16th'!K2:K41)+COUNTA('17th'!K2:K41)+COUNTA('18th'!K2:K41)+COUNTA('19th'!K2:K41)+COUNTA('20th'!K2:K41)+COUNTA('21st'!K2:K41)+COUNTA('22nd'!K2:K41)+COUNTA('23rd'!K2:K41)+COUNTA('24th'!K2:K41)+COUNTA('25th'!K2:K41)+COUNTA('26th'!K2:K41)+COUNTA('27th'!K2:K41)+COUNTA('28th'!K2:K41)+COUNTA('29th'!K2:K41)+COUNTA('30th'!K2:K41)+COUNTA('31st'!K2:K41))+0</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTA('1ST'!L2:L41)+COUNTA('2nd'!L2:L41)+COUNTA('3rd'!L2:L41)+COUNTA('4th'!L2:L41)+COUNTA('5th'!L2:L41)+COUNTA('6th'!L2:L41)+COUNTA('7th'!L2:L41)+COUNTA('8th'!L2:L41)+COUNTA('9th'!L2:L41)+COUNTA('10th'!L2:L41)+COUNTA('11th'!L2:L41)+COUNTA('12th'!L2:L41)+COUNTA('13th'!L2:L41)+COUNTA('14th'!L2:L41)+COUNTA('15th'!L2:L41)+COUNTA('16th'!L2:L41)+COUNTA('17th'!L2:L41)+COUNTA('18th'!L2:L41)+COUNTA('19th'!L2:L41)+COUNTA('20th'!L2:L41)+COUNTA('21st'!L2:L41)+COUNTA('22nd'!L2:L41)+COUNTA('23rd'!L2:L41)+COUNTA('24th'!L2:L41)+COUNTA('25th'!L2:L41)+COUNTA('26th'!L2:L41)+COUNTA('27th'!L2:L41)+COUNTA('28th'!L2:L41)+COUNTA('29th'!L2:L41)+COUNTA('30th'!L2:L41)+COUNTA('31st'!L2:L41)</f>
+        <f>(COUNTA('1ST'!L2:L41)+COUNTA('2nd'!L2:L41)+COUNTA('3rd'!L2:L41)+COUNTA('4th'!L2:L41)+COUNTA('5th'!L2:L41)+COUNTA('6th'!L2:L41)+COUNTA('7th'!L2:L41)+COUNTA('8th'!L2:L41)+COUNTA('9th'!L2:L41)+COUNTA('10th'!L2:L41)+COUNTA('11th'!L2:L41)+COUNTA('12th'!L2:L41)+COUNTA('13th'!L2:L41)+COUNTA('14th'!L2:L41)+COUNTA('15th'!L2:L41)+COUNTA('16th'!L2:L41)+COUNTA('17th'!L2:L41)+COUNTA('18th'!L2:L41)+COUNTA('19th'!L2:L41)+COUNTA('20th'!L2:L41)+COUNTA('21st'!L2:L41)+COUNTA('22nd'!L2:L41)+COUNTA('23rd'!L2:L41)+COUNTA('24th'!L2:L41)+COUNTA('25th'!L2:L41)+COUNTA('26th'!L2:L41)+COUNTA('27th'!L2:L41)+COUNTA('28th'!L2:L41)+COUNTA('29th'!L2:L41)+COUNTA('30th'!L2:L41)+COUNTA('31st'!L2:L41))+0</f>
         <v/>
       </c>
       <c r="M2" s="2">
-        <f>COUNTA('1ST'!M2:M41)+COUNTA('2nd'!M2:M41)+COUNTA('3rd'!M2:M41)+COUNTA('4th'!M2:M41)+COUNTA('5th'!M2:M41)+COUNTA('6th'!M2:M41)+COUNTA('7th'!M2:M41)+COUNTA('8th'!M2:M41)+COUNTA('9th'!M2:M41)+COUNTA('10th'!M2:M41)+COUNTA('11th'!M2:M41)+COUNTA('12th'!M2:M41)+COUNTA('13th'!M2:M41)+COUNTA('14th'!M2:M41)+COUNTA('15th'!M2:M41)+COUNTA('16th'!M2:M41)+COUNTA('17th'!M2:M41)+COUNTA('18th'!M2:M41)+COUNTA('19th'!M2:M41)+COUNTA('20th'!M2:M41)+COUNTA('21st'!M2:M41)+COUNTA('22nd'!M2:M41)+COUNTA('23rd'!M2:M41)+COUNTA('24th'!M2:M41)+COUNTA('25th'!M2:M41)+COUNTA('26th'!M2:M41)+COUNTA('27th'!M2:M41)+COUNTA('28th'!M2:M41)+COUNTA('29th'!M2:M41)+COUNTA('30th'!M2:M41)+COUNTA('31st'!M2:M41)</f>
+        <f>(COUNTA('1ST'!M2:M41)+COUNTA('2nd'!M2:M41)+COUNTA('3rd'!M2:M41)+COUNTA('4th'!M2:M41)+COUNTA('5th'!M2:M41)+COUNTA('6th'!M2:M41)+COUNTA('7th'!M2:M41)+COUNTA('8th'!M2:M41)+COUNTA('9th'!M2:M41)+COUNTA('10th'!M2:M41)+COUNTA('11th'!M2:M41)+COUNTA('12th'!M2:M41)+COUNTA('13th'!M2:M41)+COUNTA('14th'!M2:M41)+COUNTA('15th'!M2:M41)+COUNTA('16th'!M2:M41)+COUNTA('17th'!M2:M41)+COUNTA('18th'!M2:M41)+COUNTA('19th'!M2:M41)+COUNTA('20th'!M2:M41)+COUNTA('21st'!M2:M41)+COUNTA('22nd'!M2:M41)+COUNTA('23rd'!M2:M41)+COUNTA('24th'!M2:M41)+COUNTA('25th'!M2:M41)+COUNTA('26th'!M2:M41)+COUNTA('27th'!M2:M41)+COUNTA('28th'!M2:M41)+COUNTA('29th'!M2:M41)+COUNTA('30th'!M2:M41)+COUNTA('31st'!M2:M41))+0</f>
         <v/>
       </c>
       <c r="N2" s="2">
-        <f>COUNTA('1ST'!N2:N41)+COUNTA('2nd'!N2:N41)+COUNTA('3rd'!N2:N41)+COUNTA('4th'!N2:N41)+COUNTA('5th'!N2:N41)+COUNTA('6th'!N2:N41)+COUNTA('7th'!N2:N41)+COUNTA('8th'!N2:N41)+COUNTA('9th'!N2:N41)+COUNTA('10th'!N2:N41)+COUNTA('11th'!N2:N41)+COUNTA('12th'!N2:N41)+COUNTA('13th'!N2:N41)+COUNTA('14th'!N2:N41)+COUNTA('15th'!N2:N41)+COUNTA('16th'!N2:N41)+COUNTA('17th'!N2:N41)+COUNTA('18th'!N2:N41)+COUNTA('19th'!N2:N41)+COUNTA('20th'!N2:N41)+COUNTA('21st'!N2:N41)+COUNTA('22nd'!N2:N41)+COUNTA('23rd'!N2:N41)+COUNTA('24th'!N2:N41)+COUNTA('25th'!N2:N41)+COUNTA('26th'!N2:N41)+COUNTA('27th'!N2:N41)+COUNTA('28th'!N2:N41)+COUNTA('29th'!N2:N41)+COUNTA('30th'!N2:N41)+COUNTA('31st'!N2:N41)</f>
+        <f>(COUNTA('1ST'!N2:N41)+COUNTA('2nd'!N2:N41)+COUNTA('3rd'!N2:N41)+COUNTA('4th'!N2:N41)+COUNTA('5th'!N2:N41)+COUNTA('6th'!N2:N41)+COUNTA('7th'!N2:N41)+COUNTA('8th'!N2:N41)+COUNTA('9th'!N2:N41)+COUNTA('10th'!N2:N41)+COUNTA('11th'!N2:N41)+COUNTA('12th'!N2:N41)+COUNTA('13th'!N2:N41)+COUNTA('14th'!N2:N41)+COUNTA('15th'!N2:N41)+COUNTA('16th'!N2:N41)+COUNTA('17th'!N2:N41)+COUNTA('18th'!N2:N41)+COUNTA('19th'!N2:N41)+COUNTA('20th'!N2:N41)+COUNTA('21st'!N2:N41)+COUNTA('22nd'!N2:N41)+COUNTA('23rd'!N2:N41)+COUNTA('24th'!N2:N41)+COUNTA('25th'!N2:N41)+COUNTA('26th'!N2:N41)+COUNTA('27th'!N2:N41)+COUNTA('28th'!N2:N41)+COUNTA('29th'!N2:N41)+COUNTA('30th'!N2:N41)+COUNTA('31st'!N2:N41))+0</f>
         <v/>
       </c>
       <c r="O2" s="2">
-        <f>COUNTA('1ST'!O2:O41)+COUNTA('2nd'!O2:O41)+COUNTA('3rd'!O2:O41)+COUNTA('4th'!O2:O41)+COUNTA('5th'!O2:O41)+COUNTA('6th'!O2:O41)+COUNTA('7th'!O2:O41)+COUNTA('8th'!O2:O41)+COUNTA('9th'!O2:O41)+COUNTA('10th'!O2:O41)+COUNTA('11th'!O2:O41)+COUNTA('12th'!O2:O41)+COUNTA('13th'!O2:O41)+COUNTA('14th'!O2:O41)+COUNTA('15th'!O2:O41)+COUNTA('16th'!O2:O41)+COUNTA('17th'!O2:O41)+COUNTA('18th'!O2:O41)+COUNTA('19th'!O2:O41)+COUNTA('20th'!O2:O41)+COUNTA('21st'!O2:O41)+COUNTA('22nd'!O2:O41)+COUNTA('23rd'!O2:O41)+COUNTA('24th'!O2:O41)+COUNTA('25th'!O2:O41)+COUNTA('26th'!O2:O41)+COUNTA('27th'!O2:O41)+COUNTA('28th'!O2:O41)+COUNTA('29th'!O2:O41)+COUNTA('30th'!O2:O41)+COUNTA('31st'!O2:O41)</f>
+        <f>(COUNTA('1ST'!O2:O41)+COUNTA('2nd'!O2:O41)+COUNTA('3rd'!O2:O41)+COUNTA('4th'!O2:O41)+COUNTA('5th'!O2:O41)+COUNTA('6th'!O2:O41)+COUNTA('7th'!O2:O41)+COUNTA('8th'!O2:O41)+COUNTA('9th'!O2:O41)+COUNTA('10th'!O2:O41)+COUNTA('11th'!O2:O41)+COUNTA('12th'!O2:O41)+COUNTA('13th'!O2:O41)+COUNTA('14th'!O2:O41)+COUNTA('15th'!O2:O41)+COUNTA('16th'!O2:O41)+COUNTA('17th'!O2:O41)+COUNTA('18th'!O2:O41)+COUNTA('19th'!O2:O41)+COUNTA('20th'!O2:O41)+COUNTA('21st'!O2:O41)+COUNTA('22nd'!O2:O41)+COUNTA('23rd'!O2:O41)+COUNTA('24th'!O2:O41)+COUNTA('25th'!O2:O41)+COUNTA('26th'!O2:O41)+COUNTA('27th'!O2:O41)+COUNTA('28th'!O2:O41)+COUNTA('29th'!O2:O41)+COUNTA('30th'!O2:O41)+COUNTA('31st'!O2:O41))+0</f>
         <v/>
       </c>
       <c r="P2" s="2">
-        <f>COUNTA('1ST'!P2:P41)+COUNTA('2nd'!P2:P41)+COUNTA('3rd'!P2:P41)+COUNTA('4th'!P2:P41)+COUNTA('5th'!P2:P41)+COUNTA('6th'!P2:P41)+COUNTA('7th'!P2:P41)+COUNTA('8th'!P2:P41)+COUNTA('9th'!P2:P41)+COUNTA('10th'!P2:P41)+COUNTA('11th'!P2:P41)+COUNTA('12th'!P2:P41)+COUNTA('13th'!P2:P41)+COUNTA('14th'!P2:P41)+COUNTA('15th'!P2:P41)+COUNTA('16th'!P2:P41)+COUNTA('17th'!P2:P41)+COUNTA('18th'!P2:P41)+COUNTA('19th'!P2:P41)+COUNTA('20th'!P2:P41)+COUNTA('21st'!P2:P41)+COUNTA('22nd'!P2:P41)+COUNTA('23rd'!P2:P41)+COUNTA('24th'!P2:P41)+COUNTA('25th'!P2:P41)+COUNTA('26th'!P2:P41)+COUNTA('27th'!P2:P41)+COUNTA('28th'!P2:P41)+COUNTA('29th'!P2:P41)+COUNTA('30th'!P2:P41)+COUNTA('31st'!P2:P41)</f>
+        <f>(COUNTA('1ST'!P2:P41)+COUNTA('2nd'!P2:P41)+COUNTA('3rd'!P2:P41)+COUNTA('4th'!P2:P41)+COUNTA('5th'!P2:P41)+COUNTA('6th'!P2:P41)+COUNTA('7th'!P2:P41)+COUNTA('8th'!P2:P41)+COUNTA('9th'!P2:P41)+COUNTA('10th'!P2:P41)+COUNTA('11th'!P2:P41)+COUNTA('12th'!P2:P41)+COUNTA('13th'!P2:P41)+COUNTA('14th'!P2:P41)+COUNTA('15th'!P2:P41)+COUNTA('16th'!P2:P41)+COUNTA('17th'!P2:P41)+COUNTA('18th'!P2:P41)+COUNTA('19th'!P2:P41)+COUNTA('20th'!P2:P41)+COUNTA('21st'!P2:P41)+COUNTA('22nd'!P2:P41)+COUNTA('23rd'!P2:P41)+COUNTA('24th'!P2:P41)+COUNTA('25th'!P2:P41)+COUNTA('26th'!P2:P41)+COUNTA('27th'!P2:P41)+COUNTA('28th'!P2:P41)+COUNTA('29th'!P2:P41)+COUNTA('30th'!P2:P41)+COUNTA('31st'!P2:P41))+0</f>
         <v/>
       </c>
       <c r="Q2" s="2">
-        <f>COUNTA('1ST'!Q2:Q41)+COUNTA('2nd'!Q2:Q41)+COUNTA('3rd'!Q2:Q41)+COUNTA('4th'!Q2:Q41)+COUNTA('5th'!Q2:Q41)+COUNTA('6th'!Q2:Q41)+COUNTA('7th'!Q2:Q41)+COUNTA('8th'!Q2:Q41)+COUNTA('9th'!Q2:Q41)+COUNTA('10th'!Q2:Q41)+COUNTA('11th'!Q2:Q41)+COUNTA('12th'!Q2:Q41)+COUNTA('13th'!Q2:Q41)+COUNTA('14th'!Q2:Q41)+COUNTA('15th'!Q2:Q41)+COUNTA('16th'!Q2:Q41)+COUNTA('17th'!Q2:Q41)+COUNTA('18th'!Q2:Q41)+COUNTA('19th'!Q2:Q41)+COUNTA('20th'!Q2:Q41)+COUNTA('21st'!Q2:Q41)+COUNTA('22nd'!Q2:Q41)+COUNTA('23rd'!Q2:Q41)+COUNTA('24th'!Q2:Q41)+COUNTA('25th'!Q2:Q41)+COUNTA('26th'!Q2:Q41)+COUNTA('27th'!Q2:Q41)+COUNTA('28th'!Q2:Q41)+COUNTA('29th'!Q2:Q41)+COUNTA('30th'!Q2:Q41)+COUNTA('31st'!Q2:Q41)</f>
+        <f>(COUNTA('1ST'!Q2:Q41)+COUNTA('2nd'!Q2:Q41)+COUNTA('3rd'!Q2:Q41)+COUNTA('4th'!Q2:Q41)+COUNTA('5th'!Q2:Q41)+COUNTA('6th'!Q2:Q41)+COUNTA('7th'!Q2:Q41)+COUNTA('8th'!Q2:Q41)+COUNTA('9th'!Q2:Q41)+COUNTA('10th'!Q2:Q41)+COUNTA('11th'!Q2:Q41)+COUNTA('12th'!Q2:Q41)+COUNTA('13th'!Q2:Q41)+COUNTA('14th'!Q2:Q41)+COUNTA('15th'!Q2:Q41)+COUNTA('16th'!Q2:Q41)+COUNTA('17th'!Q2:Q41)+COUNTA('18th'!Q2:Q41)+COUNTA('19th'!Q2:Q41)+COUNTA('20th'!Q2:Q41)+COUNTA('21st'!Q2:Q41)+COUNTA('22nd'!Q2:Q41)+COUNTA('23rd'!Q2:Q41)+COUNTA('24th'!Q2:Q41)+COUNTA('25th'!Q2:Q41)+COUNTA('26th'!Q2:Q41)+COUNTA('27th'!Q2:Q41)+COUNTA('28th'!Q2:Q41)+COUNTA('29th'!Q2:Q41)+COUNTA('30th'!Q2:Q41)+COUNTA('31st'!Q2:Q41))+0</f>
         <v/>
       </c>
       <c r="R2" s="2">
-        <f>COUNTA('1ST'!R2:R41)+COUNTA('2nd'!R2:R41)+COUNTA('3rd'!R2:R41)+COUNTA('4th'!R2:R41)+COUNTA('5th'!R2:R41)+COUNTA('6th'!R2:R41)+COUNTA('7th'!R2:R41)+COUNTA('8th'!R2:R41)+COUNTA('9th'!R2:R41)+COUNTA('10th'!R2:R41)+COUNTA('11th'!R2:R41)+COUNTA('12th'!R2:R41)+COUNTA('13th'!R2:R41)+COUNTA('14th'!R2:R41)+COUNTA('15th'!R2:R41)+COUNTA('16th'!R2:R41)+COUNTA('17th'!R2:R41)+COUNTA('18th'!R2:R41)+COUNTA('19th'!R2:R41)+COUNTA('20th'!R2:R41)+COUNTA('21st'!R2:R41)+COUNTA('22nd'!R2:R41)+COUNTA('23rd'!R2:R41)+COUNTA('24th'!R2:R41)+COUNTA('25th'!R2:R41)+COUNTA('26th'!R2:R41)+COUNTA('27th'!R2:R41)+COUNTA('28th'!R2:R41)+COUNTA('29th'!R2:R41)+COUNTA('30th'!R2:R41)+COUNTA('31st'!R2:R41)</f>
+        <f>(COUNTA('1ST'!R2:R41)+COUNTA('2nd'!R2:R41)+COUNTA('3rd'!R2:R41)+COUNTA('4th'!R2:R41)+COUNTA('5th'!R2:R41)+COUNTA('6th'!R2:R41)+COUNTA('7th'!R2:R41)+COUNTA('8th'!R2:R41)+COUNTA('9th'!R2:R41)+COUNTA('10th'!R2:R41)+COUNTA('11th'!R2:R41)+COUNTA('12th'!R2:R41)+COUNTA('13th'!R2:R41)+COUNTA('14th'!R2:R41)+COUNTA('15th'!R2:R41)+COUNTA('16th'!R2:R41)+COUNTA('17th'!R2:R41)+COUNTA('18th'!R2:R41)+COUNTA('19th'!R2:R41)+COUNTA('20th'!R2:R41)+COUNTA('21st'!R2:R41)+COUNTA('22nd'!R2:R41)+COUNTA('23rd'!R2:R41)+COUNTA('24th'!R2:R41)+COUNTA('25th'!R2:R41)+COUNTA('26th'!R2:R41)+COUNTA('27th'!R2:R41)+COUNTA('28th'!R2:R41)+COUNTA('29th'!R2:R41)+COUNTA('30th'!R2:R41)+COUNTA('31st'!R2:R41))+0</f>
         <v/>
       </c>
       <c r="S2" s="2">
-        <f>COUNTA('1ST'!S2:S41)+COUNTA('2nd'!S2:S41)+COUNTA('3rd'!S2:S41)+COUNTA('4th'!S2:S41)+COUNTA('5th'!S2:S41)+COUNTA('6th'!S2:S41)+COUNTA('7th'!S2:S41)+COUNTA('8th'!S2:S41)+COUNTA('9th'!S2:S41)+COUNTA('10th'!S2:S41)+COUNTA('11th'!S2:S41)+COUNTA('12th'!S2:S41)+COUNTA('13th'!S2:S41)+COUNTA('14th'!S2:S41)+COUNTA('15th'!S2:S41)+COUNTA('16th'!S2:S41)+COUNTA('17th'!S2:S41)+COUNTA('18th'!S2:S41)+COUNTA('19th'!S2:S41)+COUNTA('20th'!S2:S41)+COUNTA('21st'!S2:S41)+COUNTA('22nd'!S2:S41)+COUNTA('23rd'!S2:S41)+COUNTA('24th'!S2:S41)+COUNTA('25th'!S2:S41)+COUNTA('26th'!S2:S41)+COUNTA('27th'!S2:S41)+COUNTA('28th'!S2:S41)+COUNTA('29th'!S2:S41)+COUNTA('30th'!S2:S41)+COUNTA('31st'!S2:S41)</f>
+        <f>(COUNTA('1ST'!S2:S41)+COUNTA('2nd'!S2:S41)+COUNTA('3rd'!S2:S41)+COUNTA('4th'!S2:S41)+COUNTA('5th'!S2:S41)+COUNTA('6th'!S2:S41)+COUNTA('7th'!S2:S41)+COUNTA('8th'!S2:S41)+COUNTA('9th'!S2:S41)+COUNTA('10th'!S2:S41)+COUNTA('11th'!S2:S41)+COUNTA('12th'!S2:S41)+COUNTA('13th'!S2:S41)+COUNTA('14th'!S2:S41)+COUNTA('15th'!S2:S41)+COUNTA('16th'!S2:S41)+COUNTA('17th'!S2:S41)+COUNTA('18th'!S2:S41)+COUNTA('19th'!S2:S41)+COUNTA('20th'!S2:S41)+COUNTA('21st'!S2:S41)+COUNTA('22nd'!S2:S41)+COUNTA('23rd'!S2:S41)+COUNTA('24th'!S2:S41)+COUNTA('25th'!S2:S41)+COUNTA('26th'!S2:S41)+COUNTA('27th'!S2:S41)+COUNTA('28th'!S2:S41)+COUNTA('29th'!S2:S41)+COUNTA('30th'!S2:S41)+COUNTA('31st'!S2:S41))+0</f>
         <v/>
       </c>
       <c r="T2" s="2">
-        <f>COUNTA('1ST'!T2:T41)+COUNTA('2nd'!T2:T41)+COUNTA('3rd'!T2:T41)+COUNTA('4th'!T2:T41)+COUNTA('5th'!T2:T41)+COUNTA('6th'!T2:T41)+COUNTA('7th'!T2:T41)+COUNTA('8th'!T2:T41)+COUNTA('9th'!T2:T41)+COUNTA('10th'!T2:T41)+COUNTA('11th'!T2:T41)+COUNTA('12th'!T2:T41)+COUNTA('13th'!T2:T41)+COUNTA('14th'!T2:T41)+COUNTA('15th'!T2:T41)+COUNTA('16th'!T2:T41)+COUNTA('17th'!T2:T41)+COUNTA('18th'!T2:T41)+COUNTA('19th'!T2:T41)+COUNTA('20th'!T2:T41)+COUNTA('21st'!T2:T41)+COUNTA('22nd'!T2:T41)+COUNTA('23rd'!T2:T41)+COUNTA('24th'!T2:T41)+COUNTA('25th'!T2:T41)+COUNTA('26th'!T2:T41)+COUNTA('27th'!T2:T41)+COUNTA('28th'!T2:T41)+COUNTA('29th'!T2:T41)+COUNTA('30th'!T2:T41)+COUNTA('31st'!T2:T41)</f>
+        <f>(COUNTA('1ST'!T2:T41)+COUNTA('2nd'!T2:T41)+COUNTA('3rd'!T2:T41)+COUNTA('4th'!T2:T41)+COUNTA('5th'!T2:T41)+COUNTA('6th'!T2:T41)+COUNTA('7th'!T2:T41)+COUNTA('8th'!T2:T41)+COUNTA('9th'!T2:T41)+COUNTA('10th'!T2:T41)+COUNTA('11th'!T2:T41)+COUNTA('12th'!T2:T41)+COUNTA('13th'!T2:T41)+COUNTA('14th'!T2:T41)+COUNTA('15th'!T2:T41)+COUNTA('16th'!T2:T41)+COUNTA('17th'!T2:T41)+COUNTA('18th'!T2:T41)+COUNTA('19th'!T2:T41)+COUNTA('20th'!T2:T41)+COUNTA('21st'!T2:T41)+COUNTA('22nd'!T2:T41)+COUNTA('23rd'!T2:T41)+COUNTA('24th'!T2:T41)+COUNTA('25th'!T2:T41)+COUNTA('26th'!T2:T41)+COUNTA('27th'!T2:T41)+COUNTA('28th'!T2:T41)+COUNTA('29th'!T2:T41)+COUNTA('30th'!T2:T41)+COUNTA('31st'!T2:T41))+0</f>
         <v/>
       </c>
       <c r="U2" s="2">
-        <f>COUNTA('1ST'!U2:U41)+COUNTA('2nd'!U2:U41)+COUNTA('3rd'!U2:U41)+COUNTA('4th'!U2:U41)+COUNTA('5th'!U2:U41)+COUNTA('6th'!U2:U41)+COUNTA('7th'!U2:U41)+COUNTA('8th'!U2:U41)+COUNTA('9th'!U2:U41)+COUNTA('10th'!U2:U41)+COUNTA('11th'!U2:U41)+COUNTA('12th'!U2:U41)+COUNTA('13th'!U2:U41)+COUNTA('14th'!U2:U41)+COUNTA('15th'!U2:U41)+COUNTA('16th'!U2:U41)+COUNTA('17th'!U2:U41)+COUNTA('18th'!U2:U41)+COUNTA('19th'!U2:U41)+COUNTA('20th'!U2:U41)+COUNTA('21st'!U2:U41)+COUNTA('22nd'!U2:U41)+COUNTA('23rd'!U2:U41)+COUNTA('24th'!U2:U41)+COUNTA('25th'!U2:U41)+COUNTA('26th'!U2:U41)+COUNTA('27th'!U2:U41)+COUNTA('28th'!U2:U41)+COUNTA('29th'!U2:U41)+COUNTA('30th'!U2:U41)+COUNTA('31st'!U2:U41)</f>
-        <v/>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
+        <f>(COUNTA('1ST'!U2:U41)+COUNTA('2nd'!U2:U41)+COUNTA('3rd'!U2:U41)+COUNTA('4th'!U2:U41)+COUNTA('5th'!U2:U41)+COUNTA('6th'!U2:U41)+COUNTA('7th'!U2:U41)+COUNTA('8th'!U2:U41)+COUNTA('9th'!U2:U41)+COUNTA('10th'!U2:U41)+COUNTA('11th'!U2:U41)+COUNTA('12th'!U2:U41)+COUNTA('13th'!U2:U41)+COUNTA('14th'!U2:U41)+COUNTA('15th'!U2:U41)+COUNTA('16th'!U2:U41)+COUNTA('17th'!U2:U41)+COUNTA('18th'!U2:U41)+COUNTA('19th'!U2:U41)+COUNTA('20th'!U2:U41)+COUNTA('21st'!U2:U41)+COUNTA('22nd'!U2:U41)+COUNTA('23rd'!U2:U41)+COUNTA('24th'!U2:U41)+COUNTA('25th'!U2:U41)+COUNTA('26th'!U2:U41)+COUNTA('27th'!U2:U41)+COUNTA('28th'!U2:U41)+COUNTA('29th'!U2:U41)+COUNTA('30th'!U2:U41)+COUNTA('31st'!U2:U41))+0</f>
+        <v/>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>Reported By</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>HIV</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>DBT</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>Reported By</t>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AD2" s="4" t="inlineStr">
         <is>
           <t>HIV</t>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>DBT</t>
         </is>
@@ -3090,325 +3122,406 @@
         </is>
       </c>
       <c r="C3" s="2">
-        <f>COUNTA('1ST'!C42:C81)+COUNTA('2nd'!C42:C81)+COUNTA('3rd'!C42:C81)+COUNTA('4th'!C42:C81)+COUNTA('5th'!C42:C81)+COUNTA('6th'!C42:C81)+COUNTA('7th'!C42:C81)+COUNTA('8th'!C42:C81)+COUNTA('9th'!C42:C81)+COUNTA('10th'!C42:C81)+COUNTA('11th'!C42:C81)+COUNTA('12th'!C42:C81)+COUNTA('13th'!C42:C81)+COUNTA('14th'!C42:C81)+COUNTA('15th'!C42:C81)+COUNTA('16th'!C42:C81)+COUNTA('17th'!C42:C81)+COUNTA('18th'!C42:C81)+COUNTA('19th'!C42:C81)+COUNTA('20th'!C42:C81)+COUNTA('21st'!C42:C81)+COUNTA('22nd'!C42:C81)+COUNTA('23rd'!C42:C81)+COUNTA('24th'!C42:C81)+COUNTA('25th'!C42:C81)+COUNTA('26th'!C42:C81)+COUNTA('27th'!C42:C81)+COUNTA('28th'!C42:C81)+COUNTA('29th'!C42:C81)+COUNTA('30th'!C42:C81)+COUNTA('31st'!C42:C81)</f>
+        <f>(COUNTA('1ST'!C42:C81)+COUNTA('2nd'!C42:C81)+COUNTA('3rd'!C42:C81)+COUNTA('4th'!C42:C81)+COUNTA('5th'!C42:C81)+COUNTA('6th'!C42:C81)+COUNTA('7th'!C42:C81)+COUNTA('8th'!C42:C81)+COUNTA('9th'!C42:C81)+COUNTA('10th'!C42:C81)+COUNTA('11th'!C42:C81)+COUNTA('12th'!C42:C81)+COUNTA('13th'!C42:C81)+COUNTA('14th'!C42:C81)+COUNTA('15th'!C42:C81)+COUNTA('16th'!C42:C81)+COUNTA('17th'!C42:C81)+COUNTA('18th'!C42:C81)+COUNTA('19th'!C42:C81)+COUNTA('20th'!C42:C81)+COUNTA('21st'!C42:C81)+COUNTA('22nd'!C42:C81)+COUNTA('23rd'!C42:C81)+COUNTA('24th'!C42:C81)+COUNTA('25th'!C42:C81)+COUNTA('26th'!C42:C81)+COUNTA('27th'!C42:C81)+COUNTA('28th'!C42:C81)+COUNTA('29th'!C42:C81)+COUNTA('30th'!C42:C81)+COUNTA('31st'!C42:C81))+0</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTA('1ST'!D42:D81)+COUNTA('2nd'!D42:D81)+COUNTA('3rd'!D42:D81)+COUNTA('4th'!D42:D81)+COUNTA('5th'!D42:D81)+COUNTA('6th'!D42:D81)+COUNTA('7th'!D42:D81)+COUNTA('8th'!D42:D81)+COUNTA('9th'!D42:D81)+COUNTA('10th'!D42:D81)+COUNTA('11th'!D42:D81)+COUNTA('12th'!D42:D81)+COUNTA('13th'!D42:D81)+COUNTA('14th'!D42:D81)+COUNTA('15th'!D42:D81)+COUNTA('16th'!D42:D81)+COUNTA('17th'!D42:D81)+COUNTA('18th'!D42:D81)+COUNTA('19th'!D42:D81)+COUNTA('20th'!D42:D81)+COUNTA('21st'!D42:D81)+COUNTA('22nd'!D42:D81)+COUNTA('23rd'!D42:D81)+COUNTA('24th'!D42:D81)+COUNTA('25th'!D42:D81)+COUNTA('26th'!D42:D81)+COUNTA('27th'!D42:D81)+COUNTA('28th'!D42:D81)+COUNTA('29th'!D42:D81)+COUNTA('30th'!D42:D81)+COUNTA('31st'!D42:D81)</f>
+        <f>(COUNTA('1ST'!D42:D81)+COUNTA('2nd'!D42:D81)+COUNTA('3rd'!D42:D81)+COUNTA('4th'!D42:D81)+COUNTA('5th'!D42:D81)+COUNTA('6th'!D42:D81)+COUNTA('7th'!D42:D81)+COUNTA('8th'!D42:D81)+COUNTA('9th'!D42:D81)+COUNTA('10th'!D42:D81)+COUNTA('11th'!D42:D81)+COUNTA('12th'!D42:D81)+COUNTA('13th'!D42:D81)+COUNTA('14th'!D42:D81)+COUNTA('15th'!D42:D81)+COUNTA('16th'!D42:D81)+COUNTA('17th'!D42:D81)+COUNTA('18th'!D42:D81)+COUNTA('19th'!D42:D81)+COUNTA('20th'!D42:D81)+COUNTA('21st'!D42:D81)+COUNTA('22nd'!D42:D81)+COUNTA('23rd'!D42:D81)+COUNTA('24th'!D42:D81)+COUNTA('25th'!D42:D81)+COUNTA('26th'!D42:D81)+COUNTA('27th'!D42:D81)+COUNTA('28th'!D42:D81)+COUNTA('29th'!D42:D81)+COUNTA('30th'!D42:D81)+COUNTA('31st'!D42:D81))+0</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>COUNTA('1ST'!E42:E81)+COUNTA('2nd'!E42:E81)+COUNTA('3rd'!E42:E81)+COUNTA('4th'!E42:E81)+COUNTA('5th'!E42:E81)+COUNTA('6th'!E42:E81)+COUNTA('7th'!E42:E81)+COUNTA('8th'!E42:E81)+COUNTA('9th'!E42:E81)+COUNTA('10th'!E42:E81)+COUNTA('11th'!E42:E81)+COUNTA('12th'!E42:E81)+COUNTA('13th'!E42:E81)+COUNTA('14th'!E42:E81)+COUNTA('15th'!E42:E81)+COUNTA('16th'!E42:E81)+COUNTA('17th'!E42:E81)+COUNTA('18th'!E42:E81)+COUNTA('19th'!E42:E81)+COUNTA('20th'!E42:E81)+COUNTA('21st'!E42:E81)+COUNTA('22nd'!E42:E81)+COUNTA('23rd'!E42:E81)+COUNTA('24th'!E42:E81)+COUNTA('25th'!E42:E81)+COUNTA('26th'!E42:E81)+COUNTA('27th'!E42:E81)+COUNTA('28th'!E42:E81)+COUNTA('29th'!E42:E81)+COUNTA('30th'!E42:E81)+COUNTA('31st'!E42:E81)</f>
+        <f>(COUNTA('1ST'!E42:E81)+COUNTA('2nd'!E42:E81)+COUNTA('3rd'!E42:E81)+COUNTA('4th'!E42:E81)+COUNTA('5th'!E42:E81)+COUNTA('6th'!E42:E81)+COUNTA('7th'!E42:E81)+COUNTA('8th'!E42:E81)+COUNTA('9th'!E42:E81)+COUNTA('10th'!E42:E81)+COUNTA('11th'!E42:E81)+COUNTA('12th'!E42:E81)+COUNTA('13th'!E42:E81)+COUNTA('14th'!E42:E81)+COUNTA('15th'!E42:E81)+COUNTA('16th'!E42:E81)+COUNTA('17th'!E42:E81)+COUNTA('18th'!E42:E81)+COUNTA('19th'!E42:E81)+COUNTA('20th'!E42:E81)+COUNTA('21st'!E42:E81)+COUNTA('22nd'!E42:E81)+COUNTA('23rd'!E42:E81)+COUNTA('24th'!E42:E81)+COUNTA('25th'!E42:E81)+COUNTA('26th'!E42:E81)+COUNTA('27th'!E42:E81)+COUNTA('28th'!E42:E81)+COUNTA('29th'!E42:E81)+COUNTA('30th'!E42:E81)+COUNTA('31st'!E42:E81))+0</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTA('1ST'!F42:F81)+COUNTA('2nd'!F42:F81)+COUNTA('3rd'!F42:F81)+COUNTA('4th'!F42:F81)+COUNTA('5th'!F42:F81)+COUNTA('6th'!F42:F81)+COUNTA('7th'!F42:F81)+COUNTA('8th'!F42:F81)+COUNTA('9th'!F42:F81)+COUNTA('10th'!F42:F81)+COUNTA('11th'!F42:F81)+COUNTA('12th'!F42:F81)+COUNTA('13th'!F42:F81)+COUNTA('14th'!F42:F81)+COUNTA('15th'!F42:F81)+COUNTA('16th'!F42:F81)+COUNTA('17th'!F42:F81)+COUNTA('18th'!F42:F81)+COUNTA('19th'!F42:F81)+COUNTA('20th'!F42:F81)+COUNTA('21st'!F42:F81)+COUNTA('22nd'!F42:F81)+COUNTA('23rd'!F42:F81)+COUNTA('24th'!F42:F81)+COUNTA('25th'!F42:F81)+COUNTA('26th'!F42:F81)+COUNTA('27th'!F42:F81)+COUNTA('28th'!F42:F81)+COUNTA('29th'!F42:F81)+COUNTA('30th'!F42:F81)+COUNTA('31st'!F42:F81)</f>
+        <f>(COUNTA('1ST'!F42:F81)+COUNTA('2nd'!F42:F81)+COUNTA('3rd'!F42:F81)+COUNTA('4th'!F42:F81)+COUNTA('5th'!F42:F81)+COUNTA('6th'!F42:F81)+COUNTA('7th'!F42:F81)+COUNTA('8th'!F42:F81)+COUNTA('9th'!F42:F81)+COUNTA('10th'!F42:F81)+COUNTA('11th'!F42:F81)+COUNTA('12th'!F42:F81)+COUNTA('13th'!F42:F81)+COUNTA('14th'!F42:F81)+COUNTA('15th'!F42:F81)+COUNTA('16th'!F42:F81)+COUNTA('17th'!F42:F81)+COUNTA('18th'!F42:F81)+COUNTA('19th'!F42:F81)+COUNTA('20th'!F42:F81)+COUNTA('21st'!F42:F81)+COUNTA('22nd'!F42:F81)+COUNTA('23rd'!F42:F81)+COUNTA('24th'!F42:F81)+COUNTA('25th'!F42:F81)+COUNTA('26th'!F42:F81)+COUNTA('27th'!F42:F81)+COUNTA('28th'!F42:F81)+COUNTA('29th'!F42:F81)+COUNTA('30th'!F42:F81)+COUNTA('31st'!F42:F81))+0</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTA('1ST'!G42:G81)+COUNTA('2nd'!G42:G81)+COUNTA('3rd'!G42:G81)+COUNTA('4th'!G42:G81)+COUNTA('5th'!G42:G81)+COUNTA('6th'!G42:G81)+COUNTA('7th'!G42:G81)+COUNTA('8th'!G42:G81)+COUNTA('9th'!G42:G81)+COUNTA('10th'!G42:G81)+COUNTA('11th'!G42:G81)+COUNTA('12th'!G42:G81)+COUNTA('13th'!G42:G81)+COUNTA('14th'!G42:G81)+COUNTA('15th'!G42:G81)+COUNTA('16th'!G42:G81)+COUNTA('17th'!G42:G81)+COUNTA('18th'!G42:G81)+COUNTA('19th'!G42:G81)+COUNTA('20th'!G42:G81)+COUNTA('21st'!G42:G81)+COUNTA('22nd'!G42:G81)+COUNTA('23rd'!G42:G81)+COUNTA('24th'!G42:G81)+COUNTA('25th'!G42:G81)+COUNTA('26th'!G42:G81)+COUNTA('27th'!G42:G81)+COUNTA('28th'!G42:G81)+COUNTA('29th'!G42:G81)+COUNTA('30th'!G42:G81)+COUNTA('31st'!G42:G81)</f>
+        <f>(COUNTA('1ST'!G42:G81)+COUNTA('2nd'!G42:G81)+COUNTA('3rd'!G42:G81)+COUNTA('4th'!G42:G81)+COUNTA('5th'!G42:G81)+COUNTA('6th'!G42:G81)+COUNTA('7th'!G42:G81)+COUNTA('8th'!G42:G81)+COUNTA('9th'!G42:G81)+COUNTA('10th'!G42:G81)+COUNTA('11th'!G42:G81)+COUNTA('12th'!G42:G81)+COUNTA('13th'!G42:G81)+COUNTA('14th'!G42:G81)+COUNTA('15th'!G42:G81)+COUNTA('16th'!G42:G81)+COUNTA('17th'!G42:G81)+COUNTA('18th'!G42:G81)+COUNTA('19th'!G42:G81)+COUNTA('20th'!G42:G81)+COUNTA('21st'!G42:G81)+COUNTA('22nd'!G42:G81)+COUNTA('23rd'!G42:G81)+COUNTA('24th'!G42:G81)+COUNTA('25th'!G42:G81)+COUNTA('26th'!G42:G81)+COUNTA('27th'!G42:G81)+COUNTA('28th'!G42:G81)+COUNTA('29th'!G42:G81)+COUNTA('30th'!G42:G81)+COUNTA('31st'!G42:G81))+0</f>
         <v/>
       </c>
       <c r="H3" s="2">
-        <f>COUNTA('1ST'!H42:H81)+COUNTA('2nd'!H42:H81)+COUNTA('3rd'!H42:H81)+COUNTA('4th'!H42:H81)+COUNTA('5th'!H42:H81)+COUNTA('6th'!H42:H81)+COUNTA('7th'!H42:H81)+COUNTA('8th'!H42:H81)+COUNTA('9th'!H42:H81)+COUNTA('10th'!H42:H81)+COUNTA('11th'!H42:H81)+COUNTA('12th'!H42:H81)+COUNTA('13th'!H42:H81)+COUNTA('14th'!H42:H81)+COUNTA('15th'!H42:H81)+COUNTA('16th'!H42:H81)+COUNTA('17th'!H42:H81)+COUNTA('18th'!H42:H81)+COUNTA('19th'!H42:H81)+COUNTA('20th'!H42:H81)+COUNTA('21st'!H42:H81)+COUNTA('22nd'!H42:H81)+COUNTA('23rd'!H42:H81)+COUNTA('24th'!H42:H81)+COUNTA('25th'!H42:H81)+COUNTA('26th'!H42:H81)+COUNTA('27th'!H42:H81)+COUNTA('28th'!H42:H81)+COUNTA('29th'!H42:H81)+COUNTA('30th'!H42:H81)+COUNTA('31st'!H42:H81)</f>
+        <f>(COUNTA('1ST'!H42:H81)+COUNTA('2nd'!H42:H81)+COUNTA('3rd'!H42:H81)+COUNTA('4th'!H42:H81)+COUNTA('5th'!H42:H81)+COUNTA('6th'!H42:H81)+COUNTA('7th'!H42:H81)+COUNTA('8th'!H42:H81)+COUNTA('9th'!H42:H81)+COUNTA('10th'!H42:H81)+COUNTA('11th'!H42:H81)+COUNTA('12th'!H42:H81)+COUNTA('13th'!H42:H81)+COUNTA('14th'!H42:H81)+COUNTA('15th'!H42:H81)+COUNTA('16th'!H42:H81)+COUNTA('17th'!H42:H81)+COUNTA('18th'!H42:H81)+COUNTA('19th'!H42:H81)+COUNTA('20th'!H42:H81)+COUNTA('21st'!H42:H81)+COUNTA('22nd'!H42:H81)+COUNTA('23rd'!H42:H81)+COUNTA('24th'!H42:H81)+COUNTA('25th'!H42:H81)+COUNTA('26th'!H42:H81)+COUNTA('27th'!H42:H81)+COUNTA('28th'!H42:H81)+COUNTA('29th'!H42:H81)+COUNTA('30th'!H42:H81)+COUNTA('31st'!H42:H81))+0</f>
         <v/>
       </c>
       <c r="I3" s="2">
-        <f>COUNTA('1ST'!I42:I81)+COUNTA('2nd'!I42:I81)+COUNTA('3rd'!I42:I81)+COUNTA('4th'!I42:I81)+COUNTA('5th'!I42:I81)+COUNTA('6th'!I42:I81)+COUNTA('7th'!I42:I81)+COUNTA('8th'!I42:I81)+COUNTA('9th'!I42:I81)+COUNTA('10th'!I42:I81)+COUNTA('11th'!I42:I81)+COUNTA('12th'!I42:I81)+COUNTA('13th'!I42:I81)+COUNTA('14th'!I42:I81)+COUNTA('15th'!I42:I81)+COUNTA('16th'!I42:I81)+COUNTA('17th'!I42:I81)+COUNTA('18th'!I42:I81)+COUNTA('19th'!I42:I81)+COUNTA('20th'!I42:I81)+COUNTA('21st'!I42:I81)+COUNTA('22nd'!I42:I81)+COUNTA('23rd'!I42:I81)+COUNTA('24th'!I42:I81)+COUNTA('25th'!I42:I81)+COUNTA('26th'!I42:I81)+COUNTA('27th'!I42:I81)+COUNTA('28th'!I42:I81)+COUNTA('29th'!I42:I81)+COUNTA('30th'!I42:I81)+COUNTA('31st'!I42:I81)</f>
+        <f>(COUNTA('1ST'!I42:I81)+COUNTA('2nd'!I42:I81)+COUNTA('3rd'!I42:I81)+COUNTA('4th'!I42:I81)+COUNTA('5th'!I42:I81)+COUNTA('6th'!I42:I81)+COUNTA('7th'!I42:I81)+COUNTA('8th'!I42:I81)+COUNTA('9th'!I42:I81)+COUNTA('10th'!I42:I81)+COUNTA('11th'!I42:I81)+COUNTA('12th'!I42:I81)+COUNTA('13th'!I42:I81)+COUNTA('14th'!I42:I81)+COUNTA('15th'!I42:I81)+COUNTA('16th'!I42:I81)+COUNTA('17th'!I42:I81)+COUNTA('18th'!I42:I81)+COUNTA('19th'!I42:I81)+COUNTA('20th'!I42:I81)+COUNTA('21st'!I42:I81)+COUNTA('22nd'!I42:I81)+COUNTA('23rd'!I42:I81)+COUNTA('24th'!I42:I81)+COUNTA('25th'!I42:I81)+COUNTA('26th'!I42:I81)+COUNTA('27th'!I42:I81)+COUNTA('28th'!I42:I81)+COUNTA('29th'!I42:I81)+COUNTA('30th'!I42:I81)+COUNTA('31st'!I42:I81))+0</f>
         <v/>
       </c>
       <c r="J3" s="2">
-        <f>COUNTA('1ST'!J42:J81)+COUNTA('2nd'!J42:J81)+COUNTA('3rd'!J42:J81)+COUNTA('4th'!J42:J81)+COUNTA('5th'!J42:J81)+COUNTA('6th'!J42:J81)+COUNTA('7th'!J42:J81)+COUNTA('8th'!J42:J81)+COUNTA('9th'!J42:J81)+COUNTA('10th'!J42:J81)+COUNTA('11th'!J42:J81)+COUNTA('12th'!J42:J81)+COUNTA('13th'!J42:J81)+COUNTA('14th'!J42:J81)+COUNTA('15th'!J42:J81)+COUNTA('16th'!J42:J81)+COUNTA('17th'!J42:J81)+COUNTA('18th'!J42:J81)+COUNTA('19th'!J42:J81)+COUNTA('20th'!J42:J81)+COUNTA('21st'!J42:J81)+COUNTA('22nd'!J42:J81)+COUNTA('23rd'!J42:J81)+COUNTA('24th'!J42:J81)+COUNTA('25th'!J42:J81)+COUNTA('26th'!J42:J81)+COUNTA('27th'!J42:J81)+COUNTA('28th'!J42:J81)+COUNTA('29th'!J42:J81)+COUNTA('30th'!J42:J81)+COUNTA('31st'!J42:J81)</f>
+        <f>(COUNTA('1ST'!J42:J81)+COUNTA('2nd'!J42:J81)+COUNTA('3rd'!J42:J81)+COUNTA('4th'!J42:J81)+COUNTA('5th'!J42:J81)+COUNTA('6th'!J42:J81)+COUNTA('7th'!J42:J81)+COUNTA('8th'!J42:J81)+COUNTA('9th'!J42:J81)+COUNTA('10th'!J42:J81)+COUNTA('11th'!J42:J81)+COUNTA('12th'!J42:J81)+COUNTA('13th'!J42:J81)+COUNTA('14th'!J42:J81)+COUNTA('15th'!J42:J81)+COUNTA('16th'!J42:J81)+COUNTA('17th'!J42:J81)+COUNTA('18th'!J42:J81)+COUNTA('19th'!J42:J81)+COUNTA('20th'!J42:J81)+COUNTA('21st'!J42:J81)+COUNTA('22nd'!J42:J81)+COUNTA('23rd'!J42:J81)+COUNTA('24th'!J42:J81)+COUNTA('25th'!J42:J81)+COUNTA('26th'!J42:J81)+COUNTA('27th'!J42:J81)+COUNTA('28th'!J42:J81)+COUNTA('29th'!J42:J81)+COUNTA('30th'!J42:J81)+COUNTA('31st'!J42:J81))+0</f>
         <v/>
       </c>
       <c r="K3" s="2">
-        <f>COUNTA('1ST'!K42:K81)+COUNTA('2nd'!K42:K81)+COUNTA('3rd'!K42:K81)+COUNTA('4th'!K42:K81)+COUNTA('5th'!K42:K81)+COUNTA('6th'!K42:K81)+COUNTA('7th'!K42:K81)+COUNTA('8th'!K42:K81)+COUNTA('9th'!K42:K81)+COUNTA('10th'!K42:K81)+COUNTA('11th'!K42:K81)+COUNTA('12th'!K42:K81)+COUNTA('13th'!K42:K81)+COUNTA('14th'!K42:K81)+COUNTA('15th'!K42:K81)+COUNTA('16th'!K42:K81)+COUNTA('17th'!K42:K81)+COUNTA('18th'!K42:K81)+COUNTA('19th'!K42:K81)+COUNTA('20th'!K42:K81)+COUNTA('21st'!K42:K81)+COUNTA('22nd'!K42:K81)+COUNTA('23rd'!K42:K81)+COUNTA('24th'!K42:K81)+COUNTA('25th'!K42:K81)+COUNTA('26th'!K42:K81)+COUNTA('27th'!K42:K81)+COUNTA('28th'!K42:K81)+COUNTA('29th'!K42:K81)+COUNTA('30th'!K42:K81)+COUNTA('31st'!K42:K81)</f>
+        <f>(COUNTA('1ST'!K42:K81)+COUNTA('2nd'!K42:K81)+COUNTA('3rd'!K42:K81)+COUNTA('4th'!K42:K81)+COUNTA('5th'!K42:K81)+COUNTA('6th'!K42:K81)+COUNTA('7th'!K42:K81)+COUNTA('8th'!K42:K81)+COUNTA('9th'!K42:K81)+COUNTA('10th'!K42:K81)+COUNTA('11th'!K42:K81)+COUNTA('12th'!K42:K81)+COUNTA('13th'!K42:K81)+COUNTA('14th'!K42:K81)+COUNTA('15th'!K42:K81)+COUNTA('16th'!K42:K81)+COUNTA('17th'!K42:K81)+COUNTA('18th'!K42:K81)+COUNTA('19th'!K42:K81)+COUNTA('20th'!K42:K81)+COUNTA('21st'!K42:K81)+COUNTA('22nd'!K42:K81)+COUNTA('23rd'!K42:K81)+COUNTA('24th'!K42:K81)+COUNTA('25th'!K42:K81)+COUNTA('26th'!K42:K81)+COUNTA('27th'!K42:K81)+COUNTA('28th'!K42:K81)+COUNTA('29th'!K42:K81)+COUNTA('30th'!K42:K81)+COUNTA('31st'!K42:K81))+0</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTA('1ST'!L42:L81)+COUNTA('2nd'!L42:L81)+COUNTA('3rd'!L42:L81)+COUNTA('4th'!L42:L81)+COUNTA('5th'!L42:L81)+COUNTA('6th'!L42:L81)+COUNTA('7th'!L42:L81)+COUNTA('8th'!L42:L81)+COUNTA('9th'!L42:L81)+COUNTA('10th'!L42:L81)+COUNTA('11th'!L42:L81)+COUNTA('12th'!L42:L81)+COUNTA('13th'!L42:L81)+COUNTA('14th'!L42:L81)+COUNTA('15th'!L42:L81)+COUNTA('16th'!L42:L81)+COUNTA('17th'!L42:L81)+COUNTA('18th'!L42:L81)+COUNTA('19th'!L42:L81)+COUNTA('20th'!L42:L81)+COUNTA('21st'!L42:L81)+COUNTA('22nd'!L42:L81)+COUNTA('23rd'!L42:L81)+COUNTA('24th'!L42:L81)+COUNTA('25th'!L42:L81)+COUNTA('26th'!L42:L81)+COUNTA('27th'!L42:L81)+COUNTA('28th'!L42:L81)+COUNTA('29th'!L42:L81)+COUNTA('30th'!L42:L81)+COUNTA('31st'!L42:L81)</f>
+        <f>(COUNTA('1ST'!L42:L81)+COUNTA('2nd'!L42:L81)+COUNTA('3rd'!L42:L81)+COUNTA('4th'!L42:L81)+COUNTA('5th'!L42:L81)+COUNTA('6th'!L42:L81)+COUNTA('7th'!L42:L81)+COUNTA('8th'!L42:L81)+COUNTA('9th'!L42:L81)+COUNTA('10th'!L42:L81)+COUNTA('11th'!L42:L81)+COUNTA('12th'!L42:L81)+COUNTA('13th'!L42:L81)+COUNTA('14th'!L42:L81)+COUNTA('15th'!L42:L81)+COUNTA('16th'!L42:L81)+COUNTA('17th'!L42:L81)+COUNTA('18th'!L42:L81)+COUNTA('19th'!L42:L81)+COUNTA('20th'!L42:L81)+COUNTA('21st'!L42:L81)+COUNTA('22nd'!L42:L81)+COUNTA('23rd'!L42:L81)+COUNTA('24th'!L42:L81)+COUNTA('25th'!L42:L81)+COUNTA('26th'!L42:L81)+COUNTA('27th'!L42:L81)+COUNTA('28th'!L42:L81)+COUNTA('29th'!L42:L81)+COUNTA('30th'!L42:L81)+COUNTA('31st'!L42:L81))+0</f>
         <v/>
       </c>
       <c r="M3" s="2">
-        <f>COUNTA('1ST'!M42:M81)+COUNTA('2nd'!M42:M81)+COUNTA('3rd'!M42:M81)+COUNTA('4th'!M42:M81)+COUNTA('5th'!M42:M81)+COUNTA('6th'!M42:M81)+COUNTA('7th'!M42:M81)+COUNTA('8th'!M42:M81)+COUNTA('9th'!M42:M81)+COUNTA('10th'!M42:M81)+COUNTA('11th'!M42:M81)+COUNTA('12th'!M42:M81)+COUNTA('13th'!M42:M81)+COUNTA('14th'!M42:M81)+COUNTA('15th'!M42:M81)+COUNTA('16th'!M42:M81)+COUNTA('17th'!M42:M81)+COUNTA('18th'!M42:M81)+COUNTA('19th'!M42:M81)+COUNTA('20th'!M42:M81)+COUNTA('21st'!M42:M81)+COUNTA('22nd'!M42:M81)+COUNTA('23rd'!M42:M81)+COUNTA('24th'!M42:M81)+COUNTA('25th'!M42:M81)+COUNTA('26th'!M42:M81)+COUNTA('27th'!M42:M81)+COUNTA('28th'!M42:M81)+COUNTA('29th'!M42:M81)+COUNTA('30th'!M42:M81)+COUNTA('31st'!M42:M81)</f>
+        <f>(COUNTA('1ST'!M42:M81)+COUNTA('2nd'!M42:M81)+COUNTA('3rd'!M42:M81)+COUNTA('4th'!M42:M81)+COUNTA('5th'!M42:M81)+COUNTA('6th'!M42:M81)+COUNTA('7th'!M42:M81)+COUNTA('8th'!M42:M81)+COUNTA('9th'!M42:M81)+COUNTA('10th'!M42:M81)+COUNTA('11th'!M42:M81)+COUNTA('12th'!M42:M81)+COUNTA('13th'!M42:M81)+COUNTA('14th'!M42:M81)+COUNTA('15th'!M42:M81)+COUNTA('16th'!M42:M81)+COUNTA('17th'!M42:M81)+COUNTA('18th'!M42:M81)+COUNTA('19th'!M42:M81)+COUNTA('20th'!M42:M81)+COUNTA('21st'!M42:M81)+COUNTA('22nd'!M42:M81)+COUNTA('23rd'!M42:M81)+COUNTA('24th'!M42:M81)+COUNTA('25th'!M42:M81)+COUNTA('26th'!M42:M81)+COUNTA('27th'!M42:M81)+COUNTA('28th'!M42:M81)+COUNTA('29th'!M42:M81)+COUNTA('30th'!M42:M81)+COUNTA('31st'!M42:M81))+0</f>
         <v/>
       </c>
       <c r="N3" s="2">
-        <f>COUNTA('1ST'!N42:N81)+COUNTA('2nd'!N42:N81)+COUNTA('3rd'!N42:N81)+COUNTA('4th'!N42:N81)+COUNTA('5th'!N42:N81)+COUNTA('6th'!N42:N81)+COUNTA('7th'!N42:N81)+COUNTA('8th'!N42:N81)+COUNTA('9th'!N42:N81)+COUNTA('10th'!N42:N81)+COUNTA('11th'!N42:N81)+COUNTA('12th'!N42:N81)+COUNTA('13th'!N42:N81)+COUNTA('14th'!N42:N81)+COUNTA('15th'!N42:N81)+COUNTA('16th'!N42:N81)+COUNTA('17th'!N42:N81)+COUNTA('18th'!N42:N81)+COUNTA('19th'!N42:N81)+COUNTA('20th'!N42:N81)+COUNTA('21st'!N42:N81)+COUNTA('22nd'!N42:N81)+COUNTA('23rd'!N42:N81)+COUNTA('24th'!N42:N81)+COUNTA('25th'!N42:N81)+COUNTA('26th'!N42:N81)+COUNTA('27th'!N42:N81)+COUNTA('28th'!N42:N81)+COUNTA('29th'!N42:N81)+COUNTA('30th'!N42:N81)+COUNTA('31st'!N42:N81)</f>
+        <f>(COUNTA('1ST'!N42:N81)+COUNTA('2nd'!N42:N81)+COUNTA('3rd'!N42:N81)+COUNTA('4th'!N42:N81)+COUNTA('5th'!N42:N81)+COUNTA('6th'!N42:N81)+COUNTA('7th'!N42:N81)+COUNTA('8th'!N42:N81)+COUNTA('9th'!N42:N81)+COUNTA('10th'!N42:N81)+COUNTA('11th'!N42:N81)+COUNTA('12th'!N42:N81)+COUNTA('13th'!N42:N81)+COUNTA('14th'!N42:N81)+COUNTA('15th'!N42:N81)+COUNTA('16th'!N42:N81)+COUNTA('17th'!N42:N81)+COUNTA('18th'!N42:N81)+COUNTA('19th'!N42:N81)+COUNTA('20th'!N42:N81)+COUNTA('21st'!N42:N81)+COUNTA('22nd'!N42:N81)+COUNTA('23rd'!N42:N81)+COUNTA('24th'!N42:N81)+COUNTA('25th'!N42:N81)+COUNTA('26th'!N42:N81)+COUNTA('27th'!N42:N81)+COUNTA('28th'!N42:N81)+COUNTA('29th'!N42:N81)+COUNTA('30th'!N42:N81)+COUNTA('31st'!N42:N81))+0</f>
         <v/>
       </c>
       <c r="O3" s="2">
-        <f>COUNTA('1ST'!O42:O81)+COUNTA('2nd'!O42:O81)+COUNTA('3rd'!O42:O81)+COUNTA('4th'!O42:O81)+COUNTA('5th'!O42:O81)+COUNTA('6th'!O42:O81)+COUNTA('7th'!O42:O81)+COUNTA('8th'!O42:O81)+COUNTA('9th'!O42:O81)+COUNTA('10th'!O42:O81)+COUNTA('11th'!O42:O81)+COUNTA('12th'!O42:O81)+COUNTA('13th'!O42:O81)+COUNTA('14th'!O42:O81)+COUNTA('15th'!O42:O81)+COUNTA('16th'!O42:O81)+COUNTA('17th'!O42:O81)+COUNTA('18th'!O42:O81)+COUNTA('19th'!O42:O81)+COUNTA('20th'!O42:O81)+COUNTA('21st'!O42:O81)+COUNTA('22nd'!O42:O81)+COUNTA('23rd'!O42:O81)+COUNTA('24th'!O42:O81)+COUNTA('25th'!O42:O81)+COUNTA('26th'!O42:O81)+COUNTA('27th'!O42:O81)+COUNTA('28th'!O42:O81)+COUNTA('29th'!O42:O81)+COUNTA('30th'!O42:O81)+COUNTA('31st'!O42:O81)</f>
+        <f>(COUNTA('1ST'!O42:O81)+COUNTA('2nd'!O42:O81)+COUNTA('3rd'!O42:O81)+COUNTA('4th'!O42:O81)+COUNTA('5th'!O42:O81)+COUNTA('6th'!O42:O81)+COUNTA('7th'!O42:O81)+COUNTA('8th'!O42:O81)+COUNTA('9th'!O42:O81)+COUNTA('10th'!O42:O81)+COUNTA('11th'!O42:O81)+COUNTA('12th'!O42:O81)+COUNTA('13th'!O42:O81)+COUNTA('14th'!O42:O81)+COUNTA('15th'!O42:O81)+COUNTA('16th'!O42:O81)+COUNTA('17th'!O42:O81)+COUNTA('18th'!O42:O81)+COUNTA('19th'!O42:O81)+COUNTA('20th'!O42:O81)+COUNTA('21st'!O42:O81)+COUNTA('22nd'!O42:O81)+COUNTA('23rd'!O42:O81)+COUNTA('24th'!O42:O81)+COUNTA('25th'!O42:O81)+COUNTA('26th'!O42:O81)+COUNTA('27th'!O42:O81)+COUNTA('28th'!O42:O81)+COUNTA('29th'!O42:O81)+COUNTA('30th'!O42:O81)+COUNTA('31st'!O42:O81))+0</f>
         <v/>
       </c>
       <c r="P3" s="2">
-        <f>COUNTA('1ST'!P42:P81)+COUNTA('2nd'!P42:P81)+COUNTA('3rd'!P42:P81)+COUNTA('4th'!P42:P81)+COUNTA('5th'!P42:P81)+COUNTA('6th'!P42:P81)+COUNTA('7th'!P42:P81)+COUNTA('8th'!P42:P81)+COUNTA('9th'!P42:P81)+COUNTA('10th'!P42:P81)+COUNTA('11th'!P42:P81)+COUNTA('12th'!P42:P81)+COUNTA('13th'!P42:P81)+COUNTA('14th'!P42:P81)+COUNTA('15th'!P42:P81)+COUNTA('16th'!P42:P81)+COUNTA('17th'!P42:P81)+COUNTA('18th'!P42:P81)+COUNTA('19th'!P42:P81)+COUNTA('20th'!P42:P81)+COUNTA('21st'!P42:P81)+COUNTA('22nd'!P42:P81)+COUNTA('23rd'!P42:P81)+COUNTA('24th'!P42:P81)+COUNTA('25th'!P42:P81)+COUNTA('26th'!P42:P81)+COUNTA('27th'!P42:P81)+COUNTA('28th'!P42:P81)+COUNTA('29th'!P42:P81)+COUNTA('30th'!P42:P81)+COUNTA('31st'!P42:P81)</f>
+        <f>(COUNTA('1ST'!P42:P81)+COUNTA('2nd'!P42:P81)+COUNTA('3rd'!P42:P81)+COUNTA('4th'!P42:P81)+COUNTA('5th'!P42:P81)+COUNTA('6th'!P42:P81)+COUNTA('7th'!P42:P81)+COUNTA('8th'!P42:P81)+COUNTA('9th'!P42:P81)+COUNTA('10th'!P42:P81)+COUNTA('11th'!P42:P81)+COUNTA('12th'!P42:P81)+COUNTA('13th'!P42:P81)+COUNTA('14th'!P42:P81)+COUNTA('15th'!P42:P81)+COUNTA('16th'!P42:P81)+COUNTA('17th'!P42:P81)+COUNTA('18th'!P42:P81)+COUNTA('19th'!P42:P81)+COUNTA('20th'!P42:P81)+COUNTA('21st'!P42:P81)+COUNTA('22nd'!P42:P81)+COUNTA('23rd'!P42:P81)+COUNTA('24th'!P42:P81)+COUNTA('25th'!P42:P81)+COUNTA('26th'!P42:P81)+COUNTA('27th'!P42:P81)+COUNTA('28th'!P42:P81)+COUNTA('29th'!P42:P81)+COUNTA('30th'!P42:P81)+COUNTA('31st'!P42:P81))+0</f>
         <v/>
       </c>
       <c r="Q3" s="2">
-        <f>COUNTA('1ST'!Q42:Q81)+COUNTA('2nd'!Q42:Q81)+COUNTA('3rd'!Q42:Q81)+COUNTA('4th'!Q42:Q81)+COUNTA('5th'!Q42:Q81)+COUNTA('6th'!Q42:Q81)+COUNTA('7th'!Q42:Q81)+COUNTA('8th'!Q42:Q81)+COUNTA('9th'!Q42:Q81)+COUNTA('10th'!Q42:Q81)+COUNTA('11th'!Q42:Q81)+COUNTA('12th'!Q42:Q81)+COUNTA('13th'!Q42:Q81)+COUNTA('14th'!Q42:Q81)+COUNTA('15th'!Q42:Q81)+COUNTA('16th'!Q42:Q81)+COUNTA('17th'!Q42:Q81)+COUNTA('18th'!Q42:Q81)+COUNTA('19th'!Q42:Q81)+COUNTA('20th'!Q42:Q81)+COUNTA('21st'!Q42:Q81)+COUNTA('22nd'!Q42:Q81)+COUNTA('23rd'!Q42:Q81)+COUNTA('24th'!Q42:Q81)+COUNTA('25th'!Q42:Q81)+COUNTA('26th'!Q42:Q81)+COUNTA('27th'!Q42:Q81)+COUNTA('28th'!Q42:Q81)+COUNTA('29th'!Q42:Q81)+COUNTA('30th'!Q42:Q81)+COUNTA('31st'!Q42:Q81)</f>
+        <f>(COUNTA('1ST'!Q42:Q81)+COUNTA('2nd'!Q42:Q81)+COUNTA('3rd'!Q42:Q81)+COUNTA('4th'!Q42:Q81)+COUNTA('5th'!Q42:Q81)+COUNTA('6th'!Q42:Q81)+COUNTA('7th'!Q42:Q81)+COUNTA('8th'!Q42:Q81)+COUNTA('9th'!Q42:Q81)+COUNTA('10th'!Q42:Q81)+COUNTA('11th'!Q42:Q81)+COUNTA('12th'!Q42:Q81)+COUNTA('13th'!Q42:Q81)+COUNTA('14th'!Q42:Q81)+COUNTA('15th'!Q42:Q81)+COUNTA('16th'!Q42:Q81)+COUNTA('17th'!Q42:Q81)+COUNTA('18th'!Q42:Q81)+COUNTA('19th'!Q42:Q81)+COUNTA('20th'!Q42:Q81)+COUNTA('21st'!Q42:Q81)+COUNTA('22nd'!Q42:Q81)+COUNTA('23rd'!Q42:Q81)+COUNTA('24th'!Q42:Q81)+COUNTA('25th'!Q42:Q81)+COUNTA('26th'!Q42:Q81)+COUNTA('27th'!Q42:Q81)+COUNTA('28th'!Q42:Q81)+COUNTA('29th'!Q42:Q81)+COUNTA('30th'!Q42:Q81)+COUNTA('31st'!Q42:Q81))+0</f>
         <v/>
       </c>
       <c r="R3" s="2">
-        <f>COUNTA('1ST'!R42:R81)+COUNTA('2nd'!R42:R81)+COUNTA('3rd'!R42:R81)+COUNTA('4th'!R42:R81)+COUNTA('5th'!R42:R81)+COUNTA('6th'!R42:R81)+COUNTA('7th'!R42:R81)+COUNTA('8th'!R42:R81)+COUNTA('9th'!R42:R81)+COUNTA('10th'!R42:R81)+COUNTA('11th'!R42:R81)+COUNTA('12th'!R42:R81)+COUNTA('13th'!R42:R81)+COUNTA('14th'!R42:R81)+COUNTA('15th'!R42:R81)+COUNTA('16th'!R42:R81)+COUNTA('17th'!R42:R81)+COUNTA('18th'!R42:R81)+COUNTA('19th'!R42:R81)+COUNTA('20th'!R42:R81)+COUNTA('21st'!R42:R81)+COUNTA('22nd'!R42:R81)+COUNTA('23rd'!R42:R81)+COUNTA('24th'!R42:R81)+COUNTA('25th'!R42:R81)+COUNTA('26th'!R42:R81)+COUNTA('27th'!R42:R81)+COUNTA('28th'!R42:R81)+COUNTA('29th'!R42:R81)+COUNTA('30th'!R42:R81)+COUNTA('31st'!R42:R81)</f>
+        <f>(COUNTA('1ST'!R42:R81)+COUNTA('2nd'!R42:R81)+COUNTA('3rd'!R42:R81)+COUNTA('4th'!R42:R81)+COUNTA('5th'!R42:R81)+COUNTA('6th'!R42:R81)+COUNTA('7th'!R42:R81)+COUNTA('8th'!R42:R81)+COUNTA('9th'!R42:R81)+COUNTA('10th'!R42:R81)+COUNTA('11th'!R42:R81)+COUNTA('12th'!R42:R81)+COUNTA('13th'!R42:R81)+COUNTA('14th'!R42:R81)+COUNTA('15th'!R42:R81)+COUNTA('16th'!R42:R81)+COUNTA('17th'!R42:R81)+COUNTA('18th'!R42:R81)+COUNTA('19th'!R42:R81)+COUNTA('20th'!R42:R81)+COUNTA('21st'!R42:R81)+COUNTA('22nd'!R42:R81)+COUNTA('23rd'!R42:R81)+COUNTA('24th'!R42:R81)+COUNTA('25th'!R42:R81)+COUNTA('26th'!R42:R81)+COUNTA('27th'!R42:R81)+COUNTA('28th'!R42:R81)+COUNTA('29th'!R42:R81)+COUNTA('30th'!R42:R81)+COUNTA('31st'!R42:R81))+0</f>
         <v/>
       </c>
       <c r="S3" s="2">
-        <f>COUNTA('1ST'!S42:S81)+COUNTA('2nd'!S42:S81)+COUNTA('3rd'!S42:S81)+COUNTA('4th'!S42:S81)+COUNTA('5th'!S42:S81)+COUNTA('6th'!S42:S81)+COUNTA('7th'!S42:S81)+COUNTA('8th'!S42:S81)+COUNTA('9th'!S42:S81)+COUNTA('10th'!S42:S81)+COUNTA('11th'!S42:S81)+COUNTA('12th'!S42:S81)+COUNTA('13th'!S42:S81)+COUNTA('14th'!S42:S81)+COUNTA('15th'!S42:S81)+COUNTA('16th'!S42:S81)+COUNTA('17th'!S42:S81)+COUNTA('18th'!S42:S81)+COUNTA('19th'!S42:S81)+COUNTA('20th'!S42:S81)+COUNTA('21st'!S42:S81)+COUNTA('22nd'!S42:S81)+COUNTA('23rd'!S42:S81)+COUNTA('24th'!S42:S81)+COUNTA('25th'!S42:S81)+COUNTA('26th'!S42:S81)+COUNTA('27th'!S42:S81)+COUNTA('28th'!S42:S81)+COUNTA('29th'!S42:S81)+COUNTA('30th'!S42:S81)+COUNTA('31st'!S42:S81)</f>
+        <f>(COUNTA('1ST'!S42:S81)+COUNTA('2nd'!S42:S81)+COUNTA('3rd'!S42:S81)+COUNTA('4th'!S42:S81)+COUNTA('5th'!S42:S81)+COUNTA('6th'!S42:S81)+COUNTA('7th'!S42:S81)+COUNTA('8th'!S42:S81)+COUNTA('9th'!S42:S81)+COUNTA('10th'!S42:S81)+COUNTA('11th'!S42:S81)+COUNTA('12th'!S42:S81)+COUNTA('13th'!S42:S81)+COUNTA('14th'!S42:S81)+COUNTA('15th'!S42:S81)+COUNTA('16th'!S42:S81)+COUNTA('17th'!S42:S81)+COUNTA('18th'!S42:S81)+COUNTA('19th'!S42:S81)+COUNTA('20th'!S42:S81)+COUNTA('21st'!S42:S81)+COUNTA('22nd'!S42:S81)+COUNTA('23rd'!S42:S81)+COUNTA('24th'!S42:S81)+COUNTA('25th'!S42:S81)+COUNTA('26th'!S42:S81)+COUNTA('27th'!S42:S81)+COUNTA('28th'!S42:S81)+COUNTA('29th'!S42:S81)+COUNTA('30th'!S42:S81)+COUNTA('31st'!S42:S81))+0</f>
         <v/>
       </c>
       <c r="T3" s="2">
-        <f>COUNTA('1ST'!T42:T81)+COUNTA('2nd'!T42:T81)+COUNTA('3rd'!T42:T81)+COUNTA('4th'!T42:T81)+COUNTA('5th'!T42:T81)+COUNTA('6th'!T42:T81)+COUNTA('7th'!T42:T81)+COUNTA('8th'!T42:T81)+COUNTA('9th'!T42:T81)+COUNTA('10th'!T42:T81)+COUNTA('11th'!T42:T81)+COUNTA('12th'!T42:T81)+COUNTA('13th'!T42:T81)+COUNTA('14th'!T42:T81)+COUNTA('15th'!T42:T81)+COUNTA('16th'!T42:T81)+COUNTA('17th'!T42:T81)+COUNTA('18th'!T42:T81)+COUNTA('19th'!T42:T81)+COUNTA('20th'!T42:T81)+COUNTA('21st'!T42:T81)+COUNTA('22nd'!T42:T81)+COUNTA('23rd'!T42:T81)+COUNTA('24th'!T42:T81)+COUNTA('25th'!T42:T81)+COUNTA('26th'!T42:T81)+COUNTA('27th'!T42:T81)+COUNTA('28th'!T42:T81)+COUNTA('29th'!T42:T81)+COUNTA('30th'!T42:T81)+COUNTA('31st'!T42:T81)</f>
+        <f>(COUNTA('1ST'!T42:T81)+COUNTA('2nd'!T42:T81)+COUNTA('3rd'!T42:T81)+COUNTA('4th'!T42:T81)+COUNTA('5th'!T42:T81)+COUNTA('6th'!T42:T81)+COUNTA('7th'!T42:T81)+COUNTA('8th'!T42:T81)+COUNTA('9th'!T42:T81)+COUNTA('10th'!T42:T81)+COUNTA('11th'!T42:T81)+COUNTA('12th'!T42:T81)+COUNTA('13th'!T42:T81)+COUNTA('14th'!T42:T81)+COUNTA('15th'!T42:T81)+COUNTA('16th'!T42:T81)+COUNTA('17th'!T42:T81)+COUNTA('18th'!T42:T81)+COUNTA('19th'!T42:T81)+COUNTA('20th'!T42:T81)+COUNTA('21st'!T42:T81)+COUNTA('22nd'!T42:T81)+COUNTA('23rd'!T42:T81)+COUNTA('24th'!T42:T81)+COUNTA('25th'!T42:T81)+COUNTA('26th'!T42:T81)+COUNTA('27th'!T42:T81)+COUNTA('28th'!T42:T81)+COUNTA('29th'!T42:T81)+COUNTA('30th'!T42:T81)+COUNTA('31st'!T42:T81))+0</f>
         <v/>
       </c>
       <c r="U3" s="2">
-        <f>COUNTA('1ST'!U42:U81)+COUNTA('2nd'!U42:U81)+COUNTA('3rd'!U42:U81)+COUNTA('4th'!U42:U81)+COUNTA('5th'!U42:U81)+COUNTA('6th'!U42:U81)+COUNTA('7th'!U42:U81)+COUNTA('8th'!U42:U81)+COUNTA('9th'!U42:U81)+COUNTA('10th'!U42:U81)+COUNTA('11th'!U42:U81)+COUNTA('12th'!U42:U81)+COUNTA('13th'!U42:U81)+COUNTA('14th'!U42:U81)+COUNTA('15th'!U42:U81)+COUNTA('16th'!U42:U81)+COUNTA('17th'!U42:U81)+COUNTA('18th'!U42:U81)+COUNTA('19th'!U42:U81)+COUNTA('20th'!U42:U81)+COUNTA('21st'!U42:U81)+COUNTA('22nd'!U42:U81)+COUNTA('23rd'!U42:U81)+COUNTA('24th'!U42:U81)+COUNTA('25th'!U42:U81)+COUNTA('26th'!U42:U81)+COUNTA('27th'!U42:U81)+COUNTA('28th'!U42:U81)+COUNTA('29th'!U42:U81)+COUNTA('30th'!U42:U81)+COUNTA('31st'!U42:U81)</f>
-        <v/>
-      </c>
-      <c r="W3" s="4" t="n">
+        <f>(COUNTA('1ST'!U42:U81)+COUNTA('2nd'!U42:U81)+COUNTA('3rd'!U42:U81)+COUNTA('4th'!U42:U81)+COUNTA('5th'!U42:U81)+COUNTA('6th'!U42:U81)+COUNTA('7th'!U42:U81)+COUNTA('8th'!U42:U81)+COUNTA('9th'!U42:U81)+COUNTA('10th'!U42:U81)+COUNTA('11th'!U42:U81)+COUNTA('12th'!U42:U81)+COUNTA('13th'!U42:U81)+COUNTA('14th'!U42:U81)+COUNTA('15th'!U42:U81)+COUNTA('16th'!U42:U81)+COUNTA('17th'!U42:U81)+COUNTA('18th'!U42:U81)+COUNTA('19th'!U42:U81)+COUNTA('20th'!U42:U81)+COUNTA('21st'!U42:U81)+COUNTA('22nd'!U42:U81)+COUNTA('23rd'!U42:U81)+COUNTA('24th'!U42:U81)+COUNTA('25th'!U42:U81)+COUNTA('26th'!U42:U81)+COUNTA('27th'!U42:U81)+COUNTA('28th'!U42:U81)+COUNTA('29th'!U42:U81)+COUNTA('30th'!U42:U81)+COUNTA('31st'!U42:U81))+0</f>
+        <v/>
+      </c>
+      <c r="W3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="W4" s="4" t="n">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="C4" s="3">
+        <f>SUM(C2:C3)</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>SUM(D2:D3)</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="3">
+        <f>SUM(G2:G3)</f>
+        <v/>
+      </c>
+      <c r="H4" s="3">
+        <f>SUM(H2:H3)</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>SUM(I2:I3)</f>
+        <v/>
+      </c>
+      <c r="J4" s="3">
+        <f>SUM(J2:J3)</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>SUM(K2:K3)</f>
+        <v/>
+      </c>
+      <c r="L4" s="3">
+        <f>SUM(L2:L3)</f>
+        <v/>
+      </c>
+      <c r="M4" s="3">
+        <f>SUM(M2:M3)</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>SUM(N2:N3)</f>
+        <v/>
+      </c>
+      <c r="O4" s="3">
+        <f>SUM(O2:O3)</f>
+        <v/>
+      </c>
+      <c r="P4" s="3">
+        <f>SUM(P2:P3)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="3">
+        <f>SUM(Q2:Q3)</f>
+        <v/>
+      </c>
+      <c r="R4" s="3">
+        <f>SUM(R2:R3)</f>
+        <v/>
+      </c>
+      <c r="S4" s="3">
+        <f>SUM(S2:S3)</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>SUM(T2:T3)</f>
+        <v/>
+      </c>
+      <c r="U4" s="3">
+        <f>SUM(U2:U3)</f>
+        <v/>
+      </c>
+      <c r="W4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="W5" s="4" t="n">
+      <c r="W5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="W6" s="4" t="n">
+      <c r="W6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="W8" s="4" t="n">
+      <c r="W8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="W9" s="4" t="n">
+      <c r="W9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
-      <c r="W10" s="4" t="n">
+      <c r="W10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="W11" s="4" t="n">
+      <c r="W11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="5" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="W12" s="4" t="n">
+      <c r="W12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="5" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13">
-      <c r="W13" s="4" t="n">
+      <c r="W13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="AB13" s="4" t="n">
+      <c r="AB13" s="5" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="14">
-      <c r="W14" s="4" t="n">
+      <c r="W14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="AB14" s="4" t="n">
+      <c r="AB14" s="5" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="15">
-      <c r="W15" s="4" t="n">
+      <c r="W15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AB15" s="4" t="n">
+      <c r="AB15" s="5" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="16">
-      <c r="W16" s="4" t="n">
+      <c r="W16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AB16" s="5" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="W17" s="4" t="n">
+      <c r="W17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AB17" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="W18" s="4" t="n">
+      <c r="W18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="5" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="W19" s="4" t="n">
+      <c r="W19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB19" s="4" t="n">
+      <c r="AB19" s="5" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="W20" s="4" t="n">
+      <c r="W20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="5" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="21">
-      <c r="W21" s="4" t="n">
+      <c r="W21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AB21" s="4" t="n">
+      <c r="AB21" s="5" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="22">
-      <c r="W22" s="4" t="n">
+      <c r="W22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="5" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="23">
-      <c r="W23" s="4" t="n">
+      <c r="W23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AB23" s="4" t="n">
+      <c r="AB23" s="5" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="24">
-      <c r="W24" s="4" t="n">
+      <c r="W24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AB24" s="4" t="n">
+      <c r="AB24" s="5" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="25">
-      <c r="W25" s="4" t="n">
+      <c r="W25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AB25" s="4" t="n">
+      <c r="AB25" s="5" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="26">
-      <c r="W26" s="4" t="n">
+      <c r="W26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AB26" s="4" t="n">
+      <c r="AB26" s="5" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="27">
-      <c r="W27" s="4" t="n">
+      <c r="W27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AB27" s="4" t="n">
+      <c r="AB27" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="28">
-      <c r="W28" s="4" t="n">
+      <c r="W28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AB28" s="4" t="n">
+      <c r="AB28" s="5" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="29">
-      <c r="W29" s="4" t="n">
+      <c r="W29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AB29" s="4" t="n">
+      <c r="AB29" s="5" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="30">
-      <c r="W30" s="4" t="n">
+      <c r="W30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="5" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="31">
-      <c r="W31" s="4" t="n">
+      <c r="W31" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AB31" s="4" t="n">
+      <c r="AB31" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="32">
-      <c r="W32" s="4" t="n">
+      <c r="W32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AB32" s="4" t="n">
+      <c r="AB32" s="5" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="33">
-      <c r="W33" s="4" t="n">
+      <c r="W33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AB33" s="4" t="n">
+      <c r="AB33" s="5" t="n">
         <v>31</v>
       </c>
     </row>
